--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
@@ -670,19 +670,19 @@
         <v>3059</v>
       </c>
       <c r="D2" t="n">
-        <v>1505</v>
+        <v>1698</v>
       </c>
       <c r="E2" t="n">
-        <v>49.2</v>
+        <v>55.51</v>
       </c>
       <c r="F2" t="n">
-        <v>236</v>
+        <v>279</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -697,103 +697,103 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N2" t="n">
-        <v>9.68</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1741</v>
+        <v>1977</v>
       </c>
       <c r="Q2" t="n">
-        <v>56.91</v>
+        <v>64.63</v>
       </c>
       <c r="R2" t="n">
-        <v>1516</v>
+        <v>1281</v>
       </c>
       <c r="S2" t="n">
-        <v>1858</v>
+        <v>1819</v>
       </c>
       <c r="T2" t="n">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="U2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
       </c>
       <c r="Z2" t="n">
-        <v>267</v>
+        <v>589</v>
       </c>
       <c r="AA2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AB2" t="n">
-        <v>4044</v>
+        <v>4118</v>
       </c>
       <c r="AC2" t="n">
-        <v>2491</v>
+        <v>2798</v>
       </c>
       <c r="AD2" t="n">
-        <v>1491</v>
+        <v>1283</v>
       </c>
       <c r="AE2" t="n">
-        <v>1763</v>
+        <v>1819</v>
       </c>
       <c r="AF2" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="AG2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK2" t="n">
         <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>407</v>
+        <v>589</v>
       </c>
       <c r="AM2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AN2" t="n">
-        <v>4054</v>
+        <v>4118</v>
       </c>
       <c r="AO2" t="n">
-        <v>2515</v>
+        <v>2795</v>
       </c>
       <c r="AP2" t="n">
-        <v>-985</v>
+        <v>-1059</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-750</v>
+        <v>-821</v>
       </c>
       <c r="AR2" t="n">
-        <v>-995</v>
+        <v>-1059</v>
       </c>
       <c r="AS2" t="n">
-        <v>-774</v>
+        <v>-818</v>
       </c>
     </row>
     <row r="3">
@@ -811,19 +811,19 @@
         <v>1133</v>
       </c>
       <c r="D3" t="n">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="E3" t="n">
-        <v>29.92</v>
+        <v>32.74</v>
       </c>
       <c r="F3" t="n">
         <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -838,103 +838,103 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="N3" t="n">
-        <v>7.68</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="Q3" t="n">
-        <v>34.77</v>
+        <v>37.6</v>
       </c>
       <c r="R3" t="n">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="S3" t="n">
-        <v>513</v>
+        <v>433</v>
       </c>
       <c r="T3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U3" t="n">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="AC3" t="n">
-        <v>614</v>
+        <v>661</v>
       </c>
       <c r="AD3" t="n">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="AE3" t="n">
-        <v>514</v>
+        <v>446</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AG3" t="n">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="AH3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
         <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="AO3" t="n">
-        <v>615</v>
+        <v>670</v>
       </c>
       <c r="AP3" t="n">
-        <v>-275</v>
+        <v>-277</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-220</v>
+        <v>-235</v>
       </c>
       <c r="AR3" t="n">
-        <v>-275</v>
+        <v>-277</v>
       </c>
       <c r="AS3" t="n">
-        <v>-221</v>
+        <v>-244</v>
       </c>
     </row>
     <row r="4">
@@ -952,13 +952,13 @@
         <v>4356</v>
       </c>
       <c r="D4" t="n">
-        <v>1836</v>
+        <v>2127</v>
       </c>
       <c r="E4" t="n">
-        <v>42.15</v>
+        <v>48.83</v>
       </c>
       <c r="F4" t="n">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -979,37 +979,37 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>638</v>
+        <v>694</v>
       </c>
       <c r="N4" t="n">
-        <v>14.65</v>
+        <v>15.93</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2175</v>
+        <v>2504</v>
       </c>
       <c r="Q4" t="n">
-        <v>49.93</v>
+        <v>57.48</v>
       </c>
       <c r="R4" t="n">
-        <v>2208</v>
+        <v>1831</v>
       </c>
       <c r="S4" t="n">
-        <v>3449</v>
+        <v>3389</v>
       </c>
       <c r="T4" t="n">
-        <v>92</v>
+        <v>359</v>
       </c>
       <c r="U4" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="V4" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -1018,34 +1018,34 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
+        <v>422</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6152</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4225</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1756</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3456</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>386</v>
+      </c>
+      <c r="AG4" t="n">
         <v>95</v>
       </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6010</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3715</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2208</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>3445</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>96</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>88</v>
-      </c>
       <c r="AH4" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="AI4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1054,28 +1054,28 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>95</v>
+        <v>422</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>6010</v>
+        <v>6181</v>
       </c>
       <c r="AO4" t="n">
-        <v>3714</v>
+        <v>4330</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1654</v>
+        <v>-1796</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1540</v>
+        <v>-1721</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1654</v>
+        <v>-1825</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1539</v>
+        <v>-1826</v>
       </c>
     </row>
     <row r="5">
@@ -1093,13 +1093,13 @@
         <v>2096</v>
       </c>
       <c r="D5" t="n">
-        <v>1055</v>
+        <v>1169</v>
       </c>
       <c r="E5" t="n">
-        <v>50.33</v>
+        <v>55.77</v>
       </c>
       <c r="F5" t="n">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="G5" t="n">
         <v>12</v>
@@ -1120,28 +1120,28 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="N5" t="n">
-        <v>10.45</v>
+        <v>11.12</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1264</v>
+        <v>1412</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.31</v>
+        <v>67.37</v>
       </c>
       <c r="R5" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="S5" t="n">
-        <v>1615</v>
+        <v>1675</v>
       </c>
       <c r="T5" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>250</v>
+        <v>440</v>
       </c>
       <c r="AA5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="AC5" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
       <c r="AD5" t="n">
-        <v>1070</v>
+        <v>902</v>
       </c>
       <c r="AE5" t="n">
-        <v>1620</v>
+        <v>1675</v>
       </c>
       <c r="AF5" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1189,34 +1189,34 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>246</v>
+        <v>440</v>
       </c>
       <c r="AM5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN5" t="n">
-        <v>3058</v>
+        <v>3121</v>
       </c>
       <c r="AO5" t="n">
-        <v>1988</v>
+        <v>2219</v>
       </c>
       <c r="AP5" t="n">
-        <v>-962</v>
+        <v>-1025</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-724</v>
+        <v>-807</v>
       </c>
       <c r="AR5" t="n">
-        <v>-962</v>
+        <v>-1025</v>
       </c>
       <c r="AS5" t="n">
-        <v>-724</v>
+        <v>-807</v>
       </c>
     </row>
     <row r="6">
@@ -1234,13 +1234,13 @@
         <v>861</v>
       </c>
       <c r="D6" t="n">
-        <v>326</v>
+        <v>396</v>
       </c>
       <c r="E6" t="n">
-        <v>37.86</v>
+        <v>45.99</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
@@ -1261,103 +1261,103 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="N6" t="n">
-        <v>7.08</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>372</v>
+        <v>450</v>
       </c>
       <c r="Q6" t="n">
-        <v>43.21</v>
+        <v>52.26</v>
       </c>
       <c r="R6" t="n">
-        <v>542</v>
+        <v>448</v>
       </c>
       <c r="S6" t="n">
-        <v>486</v>
+        <v>544</v>
       </c>
       <c r="T6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6" t="n">
+        <v>8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>93</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1121</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>659</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>449</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>544</v>
+      </c>
+      <c r="AF6" t="n">
         <v>5</v>
       </c>
-      <c r="X6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1105</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>550</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>543</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>490</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6</v>
-      </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1</v>
       </c>
-      <c r="AI6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2</v>
-      </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>1105</v>
+        <v>1121</v>
       </c>
       <c r="AO6" t="n">
-        <v>549</v>
+        <v>658</v>
       </c>
       <c r="AP6" t="n">
-        <v>-244</v>
+        <v>-260</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-178</v>
+        <v>-209</v>
       </c>
       <c r="AR6" t="n">
-        <v>-244</v>
+        <v>-260</v>
       </c>
       <c r="AS6" t="n">
-        <v>-177</v>
+        <v>-208</v>
       </c>
     </row>
     <row r="7">
@@ -1375,13 +1375,13 @@
         <v>716</v>
       </c>
       <c r="D7" t="n">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="E7" t="n">
-        <v>40.78</v>
+        <v>44.27</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
@@ -1402,37 +1402,37 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N7" t="n">
-        <v>8.24</v>
+        <v>8.66</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="Q7" t="n">
-        <v>50.28</v>
+        <v>55.87</v>
       </c>
       <c r="R7" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="S7" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1441,34 +1441,34 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB7" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="AC7" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="AD7" t="n">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="AE7" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -1477,28 +1477,28 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AM7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="AO7" t="n">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="AP7" t="n">
-        <v>-281</v>
+        <v>-302</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-207</v>
+        <v>-223</v>
       </c>
       <c r="AR7" t="n">
-        <v>-281</v>
+        <v>-302</v>
       </c>
       <c r="AS7" t="n">
-        <v>-207</v>
+        <v>-223</v>
       </c>
     </row>
     <row r="8">
@@ -1516,13 +1516,13 @@
         <v>3369</v>
       </c>
       <c r="D8" t="n">
-        <v>1115</v>
+        <v>1205</v>
       </c>
       <c r="E8" t="n">
-        <v>33.1</v>
+        <v>35.77</v>
       </c>
       <c r="F8" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="G8" t="n">
         <v>14</v>
@@ -1543,37 +1543,37 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="N8" t="n">
-        <v>9.59</v>
+        <v>9.85</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1392</v>
+        <v>1498</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.32</v>
+        <v>44.46</v>
       </c>
       <c r="R8" t="n">
-        <v>2210</v>
+        <v>2105</v>
       </c>
       <c r="S8" t="n">
-        <v>2073</v>
+        <v>1928</v>
       </c>
       <c r="T8" t="n">
-        <v>158</v>
+        <v>223</v>
       </c>
       <c r="U8" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>2</v>
@@ -1582,34 +1582,34 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>62</v>
+        <v>261</v>
       </c>
       <c r="AA8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4573</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2432</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1928</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>229</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>2</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4540</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2305</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2210</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2074</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>155</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
       </c>
       <c r="AJ8" t="n">
         <v>2</v>
@@ -1618,28 +1618,28 @@
         <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>61</v>
+        <v>261</v>
       </c>
       <c r="AM8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AN8" t="n">
-        <v>4539</v>
+        <v>4574</v>
       </c>
       <c r="AO8" t="n">
-        <v>2302</v>
+        <v>2438</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1171</v>
+        <v>-1204</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-913</v>
+        <v>-934</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1170</v>
+        <v>-1205</v>
       </c>
       <c r="AS8" t="n">
-        <v>-910</v>
+        <v>-940</v>
       </c>
     </row>
     <row r="9">
@@ -1657,13 +1657,13 @@
         <v>4381</v>
       </c>
       <c r="D9" t="n">
-        <v>1484</v>
+        <v>1631</v>
       </c>
       <c r="E9" t="n">
-        <v>33.87</v>
+        <v>37.23</v>
       </c>
       <c r="F9" t="n">
-        <v>342</v>
+        <v>388</v>
       </c>
       <c r="G9" t="n">
         <v>18</v>
@@ -1684,103 +1684,103 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="N9" t="n">
-        <v>6.85</v>
+        <v>7.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1826</v>
+        <v>2019</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.68</v>
+        <v>46.09</v>
       </c>
       <c r="R9" t="n">
-        <v>3079</v>
+        <v>2889</v>
       </c>
       <c r="S9" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="T9" t="n">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="U9" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="V9" t="n">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="AC9" t="n">
-        <v>2772</v>
+        <v>3042</v>
       </c>
       <c r="AD9" t="n">
-        <v>3079</v>
+        <v>2890</v>
       </c>
       <c r="AE9" t="n">
-        <v>2603</v>
+        <v>2279</v>
       </c>
       <c r="AF9" t="n">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AH9" t="n">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>17</v>
+        <v>458</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN9" t="n">
-        <v>5884</v>
+        <v>5969</v>
       </c>
       <c r="AO9" t="n">
-        <v>2772</v>
+        <v>3040</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1503</v>
+        <v>-1588</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-946</v>
+        <v>-1023</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1503</v>
+        <v>-1588</v>
       </c>
       <c r="AS9" t="n">
-        <v>-946</v>
+        <v>-1021</v>
       </c>
     </row>
     <row r="10">
@@ -1798,13 +1798,13 @@
         <v>5550</v>
       </c>
       <c r="D10" t="n">
-        <v>1786</v>
+        <v>1980</v>
       </c>
       <c r="E10" t="n">
-        <v>32.18</v>
+        <v>35.68</v>
       </c>
       <c r="F10" t="n">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="G10" t="n">
         <v>22</v>
@@ -1813,10 +1813,10 @@
         <v>0.4</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1825,34 +1825,34 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>819</v>
+        <v>852</v>
       </c>
       <c r="N10" t="n">
-        <v>14.76</v>
+        <v>15.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2244</v>
+        <v>2470</v>
       </c>
       <c r="Q10" t="n">
-        <v>40.43</v>
+        <v>44.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3915</v>
+        <v>3660</v>
       </c>
       <c r="S10" t="n">
-        <v>3813</v>
+        <v>3861</v>
       </c>
       <c r="T10" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="U10" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="V10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1864,31 +1864,31 @@
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="AA10" t="n">
         <v>3</v>
       </c>
       <c r="AB10" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="AC10" t="n">
-        <v>3900</v>
+        <v>4199</v>
       </c>
       <c r="AD10" t="n">
-        <v>3918</v>
+        <v>3661</v>
       </c>
       <c r="AE10" t="n">
-        <v>3813</v>
+        <v>3854</v>
       </c>
       <c r="AF10" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1900,28 +1900,28 @@
         <v>1</v>
       </c>
       <c r="AL10" t="n">
-        <v>25</v>
+        <v>227</v>
       </c>
       <c r="AM10" t="n">
         <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>7944</v>
+        <v>8009</v>
       </c>
       <c r="AO10" t="n">
-        <v>3900</v>
+        <v>4198</v>
       </c>
       <c r="AP10" t="n">
-        <v>-2394</v>
+        <v>-2459</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1656</v>
+        <v>-1729</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2394</v>
+        <v>-2459</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1656</v>
+        <v>-1728</v>
       </c>
     </row>
     <row r="11">
@@ -1939,19 +1939,19 @@
         <v>4040</v>
       </c>
       <c r="D11" t="n">
-        <v>1478</v>
+        <v>1618</v>
       </c>
       <c r="E11" t="n">
-        <v>36.58</v>
+        <v>40.05</v>
       </c>
       <c r="F11" t="n">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1966,37 +1966,37 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>512</v>
+        <v>563</v>
       </c>
       <c r="N11" t="n">
-        <v>12.67</v>
+        <v>13.94</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1726</v>
+        <v>1904</v>
       </c>
       <c r="Q11" t="n">
-        <v>42.72</v>
+        <v>47.13</v>
       </c>
       <c r="R11" t="n">
-        <v>2373</v>
+        <v>2154</v>
       </c>
       <c r="S11" t="n">
-        <v>2316</v>
+        <v>2397</v>
       </c>
       <c r="T11" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="U11" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="V11" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>3</v>
@@ -2005,34 +2005,34 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="AA11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="AC11" t="n">
-        <v>2591</v>
+        <v>2880</v>
       </c>
       <c r="AD11" t="n">
-        <v>2373</v>
+        <v>2159</v>
       </c>
       <c r="AE11" t="n">
-        <v>2314</v>
+        <v>2397</v>
       </c>
       <c r="AF11" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="AG11" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="AH11" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
         <v>3</v>
@@ -2041,28 +2041,28 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>116</v>
+        <v>371</v>
       </c>
       <c r="AM11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>5119</v>
+        <v>5162</v>
       </c>
       <c r="AO11" t="n">
-        <v>2591</v>
+        <v>2874</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1079</v>
+        <v>-1122</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-865</v>
+        <v>-976</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1079</v>
+        <v>-1122</v>
       </c>
       <c r="AS11" t="n">
-        <v>-865</v>
+        <v>-970</v>
       </c>
     </row>
     <row r="12">
@@ -2080,13 +2080,13 @@
         <v>2040</v>
       </c>
       <c r="D12" t="n">
-        <v>668</v>
+        <v>779</v>
       </c>
       <c r="E12" t="n">
-        <v>32.75</v>
+        <v>38.19</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
@@ -2107,103 +2107,103 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="N12" t="n">
-        <v>9.02</v>
+        <v>9.31</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>725</v>
+        <v>844</v>
       </c>
       <c r="Q12" t="n">
-        <v>35.54</v>
+        <v>41.37</v>
       </c>
       <c r="R12" t="n">
-        <v>1273</v>
+        <v>1148</v>
       </c>
       <c r="S12" t="n">
-        <v>899</v>
+        <v>800</v>
       </c>
       <c r="T12" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="AA12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AB12" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="AC12" t="n">
-        <v>1080</v>
+        <v>1216</v>
       </c>
       <c r="AD12" t="n">
-        <v>1274</v>
+        <v>1150</v>
       </c>
       <c r="AE12" t="n">
-        <v>901</v>
+        <v>800</v>
       </c>
       <c r="AF12" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="n">
         <v>30</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="AM12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AN12" t="n">
-        <v>2383</v>
+        <v>2396</v>
       </c>
       <c r="AO12" t="n">
-        <v>1079</v>
+        <v>1216</v>
       </c>
       <c r="AP12" t="n">
-        <v>-343</v>
+        <v>-356</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-355</v>
+        <v>-372</v>
       </c>
       <c r="AR12" t="n">
-        <v>-343</v>
+        <v>-356</v>
       </c>
       <c r="AS12" t="n">
-        <v>-354</v>
+        <v>-372</v>
       </c>
     </row>
     <row r="13">
@@ -2221,25 +2221,25 @@
         <v>6235</v>
       </c>
       <c r="D13" t="n">
-        <v>2657</v>
+        <v>2955</v>
       </c>
       <c r="E13" t="n">
-        <v>42.61</v>
+        <v>47.39</v>
       </c>
       <c r="F13" t="n">
-        <v>679</v>
+        <v>770</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2248,103 +2248,103 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>521</v>
+        <v>621</v>
       </c>
       <c r="N13" t="n">
-        <v>8.359999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3336</v>
+        <v>3725</v>
       </c>
       <c r="Q13" t="n">
-        <v>53.5</v>
+        <v>59.74</v>
       </c>
       <c r="R13" t="n">
-        <v>3667</v>
+        <v>3161</v>
       </c>
       <c r="S13" t="n">
-        <v>5078</v>
+        <v>5121</v>
       </c>
       <c r="T13" t="n">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="U13" t="n">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="V13" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AB13" t="n">
-        <v>9254</v>
+        <v>9452</v>
       </c>
       <c r="AC13" t="n">
-        <v>5465</v>
+        <v>6129</v>
       </c>
       <c r="AD13" t="n">
-        <v>3402</v>
+        <v>2895</v>
       </c>
       <c r="AE13" t="n">
-        <v>5075</v>
+        <v>5121</v>
       </c>
       <c r="AF13" t="n">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="AG13" t="n">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="AH13" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>185</v>
+        <v>710</v>
       </c>
       <c r="AM13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AN13" t="n">
-        <v>8899</v>
+        <v>9097</v>
       </c>
       <c r="AO13" t="n">
-        <v>5376</v>
+        <v>6041</v>
       </c>
       <c r="AP13" t="n">
-        <v>-3019</v>
+        <v>-3217</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-2129</v>
+        <v>-2404</v>
       </c>
       <c r="AR13" t="n">
-        <v>-2664</v>
+        <v>-2862</v>
       </c>
       <c r="AS13" t="n">
-        <v>-2040</v>
+        <v>-2316</v>
       </c>
     </row>
     <row r="14">
@@ -2362,13 +2362,13 @@
         <v>876</v>
       </c>
       <c r="D14" t="n">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="E14" t="n">
-        <v>55.82</v>
+        <v>60.5</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G14" t="n">
         <v>5</v>
@@ -2389,34 +2389,34 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>5.59</v>
+        <v>5.71</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="Q14" t="n">
-        <v>62.1</v>
+        <v>67.81</v>
       </c>
       <c r="R14" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="S14" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="T14" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="AC14" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="AD14" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="AE14" t="n">
-        <v>713</v>
+        <v>664</v>
       </c>
       <c r="AF14" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2464,28 +2464,28 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="AO14" t="n">
-        <v>779</v>
+        <v>833</v>
       </c>
       <c r="AP14" t="n">
-        <v>-264</v>
+        <v>-276</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-235</v>
+        <v>-239</v>
       </c>
       <c r="AR14" t="n">
-        <v>-264</v>
+        <v>-276</v>
       </c>
       <c r="AS14" t="n">
-        <v>-235</v>
+        <v>-239</v>
       </c>
     </row>
     <row r="15">
@@ -2503,13 +2503,13 @@
         <v>411</v>
       </c>
       <c r="D15" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E15" t="n">
-        <v>34.06</v>
+        <v>34.79</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -2530,31 +2530,31 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N15" t="n">
-        <v>9.73</v>
+        <v>9.98</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q15" t="n">
-        <v>42.09</v>
+        <v>43.31</v>
       </c>
       <c r="R15" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="S15" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
         <v>2</v>
@@ -2575,22 +2575,22 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="AC15" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="AD15" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AE15" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH15" t="n">
         <v>2</v>
@@ -2611,22 +2611,22 @@
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="AO15" t="n">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="AP15" t="n">
-        <v>-190</v>
+        <v>-211</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-193</v>
+        <v>-212</v>
       </c>
       <c r="AR15" t="n">
-        <v>-190</v>
+        <v>-211</v>
       </c>
       <c r="AS15" t="n">
-        <v>-193</v>
+        <v>-212</v>
       </c>
     </row>
     <row r="16">
@@ -2644,13 +2644,13 @@
         <v>2170</v>
       </c>
       <c r="D16" t="n">
-        <v>763</v>
+        <v>858</v>
       </c>
       <c r="E16" t="n">
-        <v>35.16</v>
+        <v>39.54</v>
       </c>
       <c r="F16" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G16" t="n">
         <v>14</v>
@@ -2671,103 +2671,103 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="N16" t="n">
-        <v>9.859999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>895</v>
+        <v>1009</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.24</v>
+        <v>46.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1347</v>
+        <v>1236</v>
       </c>
       <c r="S16" t="n">
-        <v>1255</v>
+        <v>1149</v>
       </c>
       <c r="T16" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
         <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>104</v>
+        <v>355</v>
       </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2753</v>
+        <v>2781</v>
       </c>
       <c r="AC16" t="n">
-        <v>1400</v>
+        <v>1541</v>
       </c>
       <c r="AD16" t="n">
-        <v>1348</v>
+        <v>1230</v>
       </c>
       <c r="AE16" t="n">
-        <v>1255</v>
+        <v>1127</v>
       </c>
       <c r="AF16" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>104</v>
+        <v>404</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN16" t="n">
-        <v>2753</v>
+        <v>2784</v>
       </c>
       <c r="AO16" t="n">
-        <v>1399</v>
+        <v>1550</v>
       </c>
       <c r="AP16" t="n">
-        <v>-583</v>
+        <v>-611</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-505</v>
+        <v>-532</v>
       </c>
       <c r="AR16" t="n">
-        <v>-583</v>
+        <v>-614</v>
       </c>
       <c r="AS16" t="n">
-        <v>-504</v>
+        <v>-541</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,227 +417,227 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Prelist Awal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ditemukan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Keluarga Baru</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Persentase Meninggal</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tidak Eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Persentase Tidak Eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Persentase Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Keluarga Khusus</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -670,19 +658,19 @@
         <v>3059</v>
       </c>
       <c r="D2" t="n">
-        <v>1698</v>
+        <v>1782</v>
       </c>
       <c r="E2" t="n">
-        <v>55.51</v>
+        <v>58.25</v>
       </c>
       <c r="F2" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -697,34 +685,34 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="N2" t="n">
-        <v>9.869999999999999</v>
+        <v>10.82</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1977</v>
+        <v>2074</v>
       </c>
       <c r="Q2" t="n">
-        <v>64.63</v>
+        <v>67.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1281</v>
+        <v>1169</v>
       </c>
       <c r="S2" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="T2" t="n">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="U2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -742,25 +730,25 @@
         <v>23</v>
       </c>
       <c r="AB2" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="AC2" t="n">
-        <v>2798</v>
+        <v>2924</v>
       </c>
       <c r="AD2" t="n">
-        <v>1283</v>
+        <v>1169</v>
       </c>
       <c r="AE2" t="n">
-        <v>1819</v>
+        <v>2221</v>
       </c>
       <c r="AF2" t="n">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="AG2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -778,22 +766,22 @@
         <v>23</v>
       </c>
       <c r="AN2" t="n">
-        <v>4118</v>
+        <v>4130</v>
       </c>
       <c r="AO2" t="n">
-        <v>2795</v>
+        <v>2924</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1059</v>
+        <v>-1071</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-821</v>
+        <v>-850</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1059</v>
+        <v>-1071</v>
       </c>
       <c r="AS2" t="n">
-        <v>-818</v>
+        <v>-850</v>
       </c>
     </row>
     <row r="3">
@@ -811,19 +799,19 @@
         <v>1133</v>
       </c>
       <c r="D3" t="n">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="E3" t="n">
-        <v>32.74</v>
+        <v>36.01</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.97</v>
+        <v>1.15</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -838,67 +826,67 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="N3" t="n">
-        <v>8.380000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="Q3" t="n">
-        <v>37.6</v>
+        <v>41.13</v>
       </c>
       <c r="R3" t="n">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="S3" t="n">
-        <v>433</v>
+        <v>507</v>
       </c>
       <c r="T3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="U3" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="AC3" t="n">
-        <v>661</v>
+        <v>744</v>
       </c>
       <c r="AD3" t="n">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="AE3" t="n">
-        <v>446</v>
+        <v>507</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AG3" t="n">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -907,34 +895,34 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AK3" t="n">
         <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="AO3" t="n">
-        <v>670</v>
+        <v>744</v>
       </c>
       <c r="AP3" t="n">
-        <v>-277</v>
+        <v>-287</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-235</v>
+        <v>-278</v>
       </c>
       <c r="AR3" t="n">
-        <v>-277</v>
+        <v>-287</v>
       </c>
       <c r="AS3" t="n">
-        <v>-244</v>
+        <v>-278</v>
       </c>
     </row>
     <row r="4">
@@ -952,13 +940,13 @@
         <v>4356</v>
       </c>
       <c r="D4" t="n">
-        <v>2127</v>
+        <v>2237</v>
       </c>
       <c r="E4" t="n">
-        <v>48.83</v>
+        <v>51.35</v>
       </c>
       <c r="F4" t="n">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -979,37 +967,37 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="N4" t="n">
-        <v>15.93</v>
+        <v>16.39</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2504</v>
+        <v>2639</v>
       </c>
       <c r="Q4" t="n">
-        <v>57.48</v>
+        <v>60.58</v>
       </c>
       <c r="R4" t="n">
-        <v>1831</v>
+        <v>1605</v>
       </c>
       <c r="S4" t="n">
-        <v>3389</v>
+        <v>3789</v>
       </c>
       <c r="T4" t="n">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="U4" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="V4" t="n">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -1018,34 +1006,34 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>6152</v>
+        <v>6241</v>
       </c>
       <c r="AC4" t="n">
-        <v>4225</v>
+        <v>4550</v>
       </c>
       <c r="AD4" t="n">
-        <v>1756</v>
+        <v>1605</v>
       </c>
       <c r="AE4" t="n">
-        <v>3456</v>
+        <v>3789</v>
       </c>
       <c r="AF4" t="n">
-        <v>386</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AH4" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1054,28 +1042,28 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>422</v>
+        <v>543</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>6181</v>
+        <v>6240</v>
       </c>
       <c r="AO4" t="n">
-        <v>4330</v>
+        <v>4550</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1796</v>
+        <v>-1885</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1721</v>
+        <v>-1911</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1825</v>
+        <v>-1884</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1826</v>
+        <v>-1911</v>
       </c>
     </row>
     <row r="5">
@@ -1093,19 +1081,19 @@
         <v>2096</v>
       </c>
       <c r="D5" t="n">
-        <v>1169</v>
+        <v>1235</v>
       </c>
       <c r="E5" t="n">
-        <v>55.77</v>
+        <v>58.92</v>
       </c>
       <c r="F5" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1120,34 +1108,34 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N5" t="n">
-        <v>11.12</v>
+        <v>11.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1412</v>
+        <v>1495</v>
       </c>
       <c r="Q5" t="n">
-        <v>67.37</v>
+        <v>71.33</v>
       </c>
       <c r="R5" t="n">
-        <v>902</v>
+        <v>805</v>
       </c>
       <c r="S5" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="T5" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1165,25 +1153,25 @@
         <v>8</v>
       </c>
       <c r="AB5" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="AC5" t="n">
-        <v>2219</v>
+        <v>2353</v>
       </c>
       <c r="AD5" t="n">
-        <v>902</v>
+        <v>806</v>
       </c>
       <c r="AE5" t="n">
-        <v>1675</v>
+        <v>1886</v>
       </c>
       <c r="AF5" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1201,22 +1189,22 @@
         <v>8</v>
       </c>
       <c r="AN5" t="n">
-        <v>3121</v>
+        <v>3158</v>
       </c>
       <c r="AO5" t="n">
-        <v>2219</v>
+        <v>2352</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1025</v>
+        <v>-1062</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-807</v>
+        <v>-858</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1025</v>
+        <v>-1062</v>
       </c>
       <c r="AS5" t="n">
-        <v>-807</v>
+        <v>-857</v>
       </c>
     </row>
     <row r="6">
@@ -1234,13 +1222,13 @@
         <v>861</v>
       </c>
       <c r="D6" t="n">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="E6" t="n">
-        <v>45.99</v>
+        <v>48.08</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
@@ -1261,34 +1249,34 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N6" t="n">
-        <v>8.710000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="Q6" t="n">
-        <v>52.26</v>
+        <v>54.94</v>
       </c>
       <c r="R6" t="n">
-        <v>448</v>
+        <v>421</v>
       </c>
       <c r="S6" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="U6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1306,25 +1294,25 @@
         <v>8</v>
       </c>
       <c r="AB6" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="AC6" t="n">
-        <v>659</v>
+        <v>693</v>
       </c>
       <c r="AD6" t="n">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="AE6" t="n">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="AF6" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1342,22 +1330,22 @@
         <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="AO6" t="n">
-        <v>658</v>
+        <v>692</v>
       </c>
       <c r="AP6" t="n">
-        <v>-260</v>
+        <v>-273</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-209</v>
+        <v>-220</v>
       </c>
       <c r="AR6" t="n">
-        <v>-260</v>
+        <v>-273</v>
       </c>
       <c r="AS6" t="n">
-        <v>-208</v>
+        <v>-219</v>
       </c>
     </row>
     <row r="7">
@@ -1375,13 +1363,13 @@
         <v>716</v>
       </c>
       <c r="D7" t="n">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="E7" t="n">
-        <v>44.27</v>
+        <v>45.95</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
@@ -1402,40 +1390,40 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N7" t="n">
-        <v>8.66</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="Q7" t="n">
-        <v>55.87</v>
+        <v>57.96</v>
       </c>
       <c r="R7" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="S7" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="T7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1447,31 +1435,31 @@
         <v>4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AC7" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AD7" t="n">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="AE7" t="n">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="AF7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1483,22 +1471,22 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="AO7" t="n">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AP7" t="n">
-        <v>-302</v>
+        <v>-303</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-223</v>
+        <v>-219</v>
       </c>
       <c r="AR7" t="n">
-        <v>-302</v>
+        <v>-303</v>
       </c>
       <c r="AS7" t="n">
-        <v>-223</v>
+        <v>-219</v>
       </c>
     </row>
     <row r="8">
@@ -1516,13 +1504,13 @@
         <v>3369</v>
       </c>
       <c r="D8" t="n">
-        <v>1205</v>
+        <v>1239</v>
       </c>
       <c r="E8" t="n">
-        <v>35.77</v>
+        <v>36.78</v>
       </c>
       <c r="F8" t="n">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="G8" t="n">
         <v>14</v>
@@ -1543,37 +1531,37 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="N8" t="n">
-        <v>9.85</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1498</v>
+        <v>1547</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.46</v>
+        <v>45.92</v>
       </c>
       <c r="R8" t="n">
-        <v>2105</v>
+        <v>2049</v>
       </c>
       <c r="S8" t="n">
-        <v>1928</v>
+        <v>1986</v>
       </c>
       <c r="T8" t="n">
         <v>223</v>
       </c>
       <c r="U8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>2</v>
@@ -1582,34 +1570,34 @@
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AA8" t="n">
         <v>9</v>
       </c>
       <c r="AB8" t="n">
-        <v>4573</v>
+        <v>4596</v>
       </c>
       <c r="AC8" t="n">
-        <v>2432</v>
+        <v>2510</v>
       </c>
       <c r="AD8" t="n">
-        <v>2100</v>
+        <v>2049</v>
       </c>
       <c r="AE8" t="n">
-        <v>1928</v>
+        <v>1990</v>
       </c>
       <c r="AF8" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="AG8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>2</v>
@@ -1618,28 +1606,28 @@
         <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AM8" t="n">
         <v>9</v>
       </c>
       <c r="AN8" t="n">
-        <v>4574</v>
+        <v>4596</v>
       </c>
       <c r="AO8" t="n">
-        <v>2438</v>
+        <v>2510</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1204</v>
+        <v>-1227</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-934</v>
+        <v>-963</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1205</v>
+        <v>-1227</v>
       </c>
       <c r="AS8" t="n">
-        <v>-940</v>
+        <v>-963</v>
       </c>
     </row>
     <row r="9">
@@ -1657,13 +1645,13 @@
         <v>4381</v>
       </c>
       <c r="D9" t="n">
-        <v>1631</v>
+        <v>1696</v>
       </c>
       <c r="E9" t="n">
-        <v>37.23</v>
+        <v>38.71</v>
       </c>
       <c r="F9" t="n">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="G9" t="n">
         <v>18</v>
@@ -1684,103 +1672,103 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N9" t="n">
-        <v>7.08</v>
+        <v>7.24</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2019</v>
+        <v>2101</v>
       </c>
       <c r="Q9" t="n">
-        <v>46.09</v>
+        <v>47.96</v>
       </c>
       <c r="R9" t="n">
-        <v>2889</v>
+        <v>2813</v>
       </c>
       <c r="S9" t="n">
-        <v>2279</v>
+        <v>2427</v>
       </c>
       <c r="T9" t="n">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="U9" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="AC9" t="n">
-        <v>3042</v>
+        <v>3149</v>
       </c>
       <c r="AD9" t="n">
-        <v>2890</v>
+        <v>2808</v>
       </c>
       <c r="AE9" t="n">
-        <v>2279</v>
+        <v>2424</v>
       </c>
       <c r="AF9" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="AG9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AH9" t="n">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>458</v>
+        <v>531</v>
       </c>
       <c r="AM9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>5969</v>
+        <v>5997</v>
       </c>
       <c r="AO9" t="n">
-        <v>3040</v>
+        <v>3152</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1588</v>
+        <v>-1616</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1023</v>
+        <v>-1048</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1588</v>
+        <v>-1616</v>
       </c>
       <c r="AS9" t="n">
-        <v>-1021</v>
+        <v>-1051</v>
       </c>
     </row>
     <row r="10">
@@ -1798,13 +1786,13 @@
         <v>5550</v>
       </c>
       <c r="D10" t="n">
-        <v>1980</v>
+        <v>2064</v>
       </c>
       <c r="E10" t="n">
-        <v>35.68</v>
+        <v>37.19</v>
       </c>
       <c r="F10" t="n">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="G10" t="n">
         <v>22</v>
@@ -1825,34 +1813,34 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="N10" t="n">
-        <v>15.35</v>
+        <v>15.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2470</v>
+        <v>2581</v>
       </c>
       <c r="Q10" t="n">
-        <v>44.5</v>
+        <v>46.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3660</v>
+        <v>3560</v>
       </c>
       <c r="S10" t="n">
-        <v>3861</v>
+        <v>3868</v>
       </c>
       <c r="T10" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="U10" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1864,31 +1852,31 @@
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>228</v>
+        <v>456</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="AC10" t="n">
-        <v>4199</v>
+        <v>4368</v>
       </c>
       <c r="AD10" t="n">
-        <v>3661</v>
+        <v>3560</v>
       </c>
       <c r="AE10" t="n">
-        <v>3854</v>
+        <v>3868</v>
       </c>
       <c r="AF10" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1900,28 +1888,28 @@
         <v>1</v>
       </c>
       <c r="AL10" t="n">
-        <v>227</v>
+        <v>456</v>
       </c>
       <c r="AM10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>8009</v>
+        <v>8064</v>
       </c>
       <c r="AO10" t="n">
-        <v>4198</v>
+        <v>4368</v>
       </c>
       <c r="AP10" t="n">
-        <v>-2459</v>
+        <v>-2514</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1729</v>
+        <v>-1787</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2459</v>
+        <v>-2514</v>
       </c>
       <c r="AS10" t="n">
-        <v>-1728</v>
+        <v>-1787</v>
       </c>
     </row>
     <row r="11">
@@ -1939,13 +1927,13 @@
         <v>4040</v>
       </c>
       <c r="D11" t="n">
-        <v>1618</v>
+        <v>1669</v>
       </c>
       <c r="E11" t="n">
-        <v>40.05</v>
+        <v>41.31</v>
       </c>
       <c r="F11" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="G11" t="n">
         <v>24</v>
@@ -1966,40 +1954,40 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="N11" t="n">
-        <v>13.94</v>
+        <v>14.38</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1904</v>
+        <v>1969</v>
       </c>
       <c r="Q11" t="n">
-        <v>47.13</v>
+        <v>48.74</v>
       </c>
       <c r="R11" t="n">
-        <v>2154</v>
+        <v>2077</v>
       </c>
       <c r="S11" t="n">
-        <v>2397</v>
+        <v>2487</v>
       </c>
       <c r="T11" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="U11" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="V11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2011,31 +1999,31 @@
         <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="AC11" t="n">
-        <v>2880</v>
+        <v>2983</v>
       </c>
       <c r="AD11" t="n">
-        <v>2159</v>
+        <v>2077</v>
       </c>
       <c r="AE11" t="n">
-        <v>2397</v>
+        <v>2487</v>
       </c>
       <c r="AF11" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="AG11" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="AH11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2047,22 +2035,22 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>5162</v>
+        <v>5177</v>
       </c>
       <c r="AO11" t="n">
-        <v>2874</v>
+        <v>2983</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1122</v>
+        <v>-1137</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-976</v>
+        <v>-1014</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1122</v>
+        <v>-1137</v>
       </c>
       <c r="AS11" t="n">
-        <v>-970</v>
+        <v>-1014</v>
       </c>
     </row>
     <row r="12">
@@ -2080,13 +2068,13 @@
         <v>2040</v>
       </c>
       <c r="D12" t="n">
-        <v>779</v>
+        <v>811</v>
       </c>
       <c r="E12" t="n">
-        <v>38.19</v>
+        <v>39.75</v>
       </c>
       <c r="F12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
@@ -2107,37 +2095,37 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N12" t="n">
-        <v>9.31</v>
+        <v>9.41</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>880</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1115</v>
+      </c>
+      <c r="S12" t="n">
         <v>844</v>
       </c>
-      <c r="Q12" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1148</v>
-      </c>
-      <c r="S12" t="n">
-        <v>800</v>
-      </c>
       <c r="T12" t="n">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="V12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>3</v>
@@ -2146,34 +2134,34 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA12" t="n">
         <v>16</v>
       </c>
       <c r="AB12" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="AC12" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
       <c r="AD12" t="n">
-        <v>1150</v>
+        <v>1115</v>
       </c>
       <c r="AE12" t="n">
-        <v>800</v>
+        <v>841</v>
       </c>
       <c r="AF12" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AH12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="AI12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>3</v>
@@ -2182,28 +2170,28 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM12" t="n">
         <v>16</v>
       </c>
       <c r="AN12" t="n">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="AO12" t="n">
-        <v>1216</v>
+        <v>1266</v>
       </c>
       <c r="AP12" t="n">
-        <v>-356</v>
+        <v>-366</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-372</v>
+        <v>-386</v>
       </c>
       <c r="AR12" t="n">
-        <v>-356</v>
+        <v>-366</v>
       </c>
       <c r="AS12" t="n">
-        <v>-372</v>
+        <v>-386</v>
       </c>
     </row>
     <row r="13">
@@ -2221,25 +2209,25 @@
         <v>6235</v>
       </c>
       <c r="D13" t="n">
-        <v>2955</v>
+        <v>3168</v>
       </c>
       <c r="E13" t="n">
-        <v>47.39</v>
+        <v>50.81</v>
       </c>
       <c r="F13" t="n">
-        <v>770</v>
+        <v>820</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2248,37 +2236,37 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="N13" t="n">
-        <v>9.960000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3725</v>
+        <v>3988</v>
       </c>
       <c r="Q13" t="n">
-        <v>59.74</v>
+        <v>63.96</v>
       </c>
       <c r="R13" t="n">
-        <v>3161</v>
+        <v>2948</v>
       </c>
       <c r="S13" t="n">
-        <v>5121</v>
+        <v>5564</v>
       </c>
       <c r="T13" t="n">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="U13" t="n">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="V13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
@@ -2287,34 +2275,34 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="AA13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB13" t="n">
-        <v>9452</v>
+        <v>9558</v>
       </c>
       <c r="AC13" t="n">
-        <v>6129</v>
+        <v>6511</v>
       </c>
       <c r="AD13" t="n">
-        <v>2895</v>
+        <v>2682</v>
       </c>
       <c r="AE13" t="n">
-        <v>5121</v>
+        <v>5561</v>
       </c>
       <c r="AF13" t="n">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="AG13" t="n">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="AH13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
         <v>11</v>
@@ -2323,28 +2311,28 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="AM13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AN13" t="n">
-        <v>9097</v>
+        <v>9203</v>
       </c>
       <c r="AO13" t="n">
-        <v>6041</v>
+        <v>6424</v>
       </c>
       <c r="AP13" t="n">
-        <v>-3217</v>
+        <v>-3323</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-2404</v>
+        <v>-2523</v>
       </c>
       <c r="AR13" t="n">
-        <v>-2862</v>
+        <v>-2968</v>
       </c>
       <c r="AS13" t="n">
-        <v>-2316</v>
+        <v>-2436</v>
       </c>
     </row>
     <row r="14">
@@ -2362,13 +2350,13 @@
         <v>876</v>
       </c>
       <c r="D14" t="n">
-        <v>530</v>
+        <v>563</v>
       </c>
       <c r="E14" t="n">
-        <v>60.5</v>
+        <v>64.27</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G14" t="n">
         <v>5</v>
@@ -2389,28 +2377,28 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N14" t="n">
-        <v>5.71</v>
+        <v>5.94</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>594</v>
+        <v>629</v>
       </c>
       <c r="Q14" t="n">
-        <v>67.81</v>
+        <v>71.8</v>
       </c>
       <c r="R14" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="S14" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="T14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2434,19 +2422,19 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AC14" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
       <c r="AD14" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="AE14" t="n">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2470,22 +2458,22 @@
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="AO14" t="n">
-        <v>833</v>
+        <v>886</v>
       </c>
       <c r="AP14" t="n">
-        <v>-276</v>
+        <v>-279</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-239</v>
+        <v>-257</v>
       </c>
       <c r="AR14" t="n">
-        <v>-276</v>
+        <v>-279</v>
       </c>
       <c r="AS14" t="n">
-        <v>-239</v>
+        <v>-257</v>
       </c>
     </row>
     <row r="15">
@@ -2503,10 +2491,10 @@
         <v>411</v>
       </c>
       <c r="D15" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E15" t="n">
-        <v>34.79</v>
+        <v>35.52</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
@@ -2530,34 +2518,34 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N15" t="n">
-        <v>9.98</v>
+        <v>10.22</v>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q15" t="n">
-        <v>43.31</v>
+        <v>44.04</v>
       </c>
       <c r="R15" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="S15" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="T15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2572,28 +2560,28 @@
         <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>622</v>
       </c>
       <c r="AC15" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AD15" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AE15" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>5</v>
       </c>
       <c r="AH15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2608,25 +2596,25 @@
         <v>20</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
         <v>622</v>
       </c>
       <c r="AO15" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AP15" t="n">
         <v>-211</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
       <c r="AR15" t="n">
         <v>-211</v>
       </c>
       <c r="AS15" t="n">
-        <v>-212</v>
+        <v>-213</v>
       </c>
     </row>
     <row r="16">
@@ -2644,13 +2632,13 @@
         <v>2170</v>
       </c>
       <c r="D16" t="n">
-        <v>858</v>
+        <v>907</v>
       </c>
       <c r="E16" t="n">
-        <v>39.54</v>
+        <v>41.8</v>
       </c>
       <c r="F16" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G16" t="n">
         <v>14</v>
@@ -2671,103 +2659,103 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N16" t="n">
-        <v>10.46</v>
+        <v>10.55</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>1009</v>
+        <v>1067</v>
       </c>
       <c r="Q16" t="n">
-        <v>46.5</v>
+        <v>49.17</v>
       </c>
       <c r="R16" t="n">
-        <v>1236</v>
+        <v>1162</v>
       </c>
       <c r="S16" t="n">
-        <v>1149</v>
+        <v>1195</v>
       </c>
       <c r="T16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="W16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="AA16" t="n">
         <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2781</v>
+        <v>2805</v>
       </c>
       <c r="AC16" t="n">
-        <v>1541</v>
+        <v>1640</v>
       </c>
       <c r="AD16" t="n">
-        <v>1230</v>
+        <v>1163</v>
       </c>
       <c r="AE16" t="n">
-        <v>1127</v>
+        <v>1195</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AM16" t="n">
         <v>3</v>
       </c>
       <c r="AN16" t="n">
-        <v>2784</v>
+        <v>2804</v>
       </c>
       <c r="AO16" t="n">
-        <v>1550</v>
+        <v>1638</v>
       </c>
       <c r="AP16" t="n">
-        <v>-611</v>
+        <v>-635</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-532</v>
+        <v>-573</v>
       </c>
       <c r="AR16" t="n">
-        <v>-614</v>
+        <v>-634</v>
       </c>
       <c r="AS16" t="n">
-        <v>-541</v>
+        <v>-571</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS16"/>
+  <dimension ref="A1:AR16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,155 +489,150 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Keluarga Khusus</t>
+          <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Total Hasil Pendataan ((4) + (5))</t>
+          <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
+          <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_OPEN</t>
+          <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
+          <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
+          <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_DRAFT</t>
+          <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
+          <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
+          <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
+          <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
+          <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
+          <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
+          <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
+          <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Scraped_Pencacah_Realisasi_Scraped</t>
+          <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_OPEN</t>
+          <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
+          <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
+          <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_DRAFT</t>
+          <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
+          <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
+          <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
+          <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
+          <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
+          <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
+          <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
+          <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>Scraped_Pengawas_Realisasi_Scraped</t>
+          <t>Diff_Target_Pencacah</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>Diff_Target_Pencacah</t>
+          <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>Diff_Realisasi_Pencacah</t>
+          <t>Diff_Target_Pengawas</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
-        <is>
-          <t>Diff_Target_Pengawas</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -658,25 +653,25 @@
         <v>3059</v>
       </c>
       <c r="D2" t="n">
-        <v>1782</v>
+        <v>2156</v>
       </c>
       <c r="E2" t="n">
-        <v>58.25</v>
+        <v>70.48</v>
       </c>
       <c r="F2" t="n">
-        <v>292</v>
+        <v>390</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.49</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -685,103 +680,100 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>331</v>
+        <v>408</v>
       </c>
       <c r="N2" t="n">
-        <v>10.82</v>
+        <v>13.34</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2546</v>
       </c>
       <c r="P2" t="n">
-        <v>2074</v>
+        <v>83.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>67.8</v>
+        <v>643</v>
       </c>
       <c r="R2" t="n">
-        <v>1169</v>
+        <v>2752</v>
       </c>
       <c r="S2" t="n">
-        <v>2221</v>
+        <v>40</v>
       </c>
       <c r="T2" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="U2" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
+        <v>730</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4258</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3560</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>643</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2754</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>3</v>
       </c>
-      <c r="Z2" t="n">
-        <v>589</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4130</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2924</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1169</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2221</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>72</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>37</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>6</v>
-      </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>730</v>
       </c>
       <c r="AL2" t="n">
-        <v>589</v>
+        <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>23</v>
+        <v>4258</v>
       </c>
       <c r="AN2" t="n">
-        <v>4130</v>
+        <v>3560</v>
       </c>
       <c r="AO2" t="n">
-        <v>2924</v>
+        <v>-1199</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1071</v>
+        <v>-1014</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-850</v>
+        <v>-1199</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1071</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-850</v>
+        <v>-1014</v>
       </c>
     </row>
     <row r="3">
@@ -799,19 +791,19 @@
         <v>1133</v>
       </c>
       <c r="D3" t="n">
-        <v>408</v>
+        <v>638</v>
       </c>
       <c r="E3" t="n">
-        <v>36.01</v>
+        <v>56.31</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>1.15</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -826,103 +818,100 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="N3" t="n">
-        <v>9.710000000000001</v>
+        <v>15.09</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>746</v>
       </c>
       <c r="P3" t="n">
-        <v>466</v>
+        <v>65.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.13</v>
+        <v>184</v>
       </c>
       <c r="R3" t="n">
-        <v>410</v>
+        <v>857</v>
       </c>
       <c r="S3" t="n">
-        <v>507</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>27</v>
+        <v>199</v>
       </c>
       <c r="U3" t="n">
-        <v>266</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>212</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1490</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1107</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>184</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>857</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>199</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>4</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AJ3" t="n">
         <v>1</v>
       </c>
-      <c r="Z3" t="n">
-        <v>202</v>
-      </c>
-      <c r="AA3" t="n">
+      <c r="AK3" t="n">
+        <v>212</v>
+      </c>
+      <c r="AL3" t="n">
         <v>3</v>
       </c>
-      <c r="AB3" t="n">
-        <v>1420</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>744</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>410</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>507</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>266</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>202</v>
-      </c>
       <c r="AM3" t="n">
-        <v>3</v>
+        <v>1490</v>
       </c>
       <c r="AN3" t="n">
-        <v>1420</v>
+        <v>1107</v>
       </c>
       <c r="AO3" t="n">
-        <v>744</v>
+        <v>-357</v>
       </c>
       <c r="AP3" t="n">
-        <v>-287</v>
+        <v>-361</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-278</v>
+        <v>-357</v>
       </c>
       <c r="AR3" t="n">
-        <v>-287</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-278</v>
+        <v>-361</v>
       </c>
     </row>
     <row r="4">
@@ -940,13 +929,13 @@
         <v>4356</v>
       </c>
       <c r="D4" t="n">
-        <v>2237</v>
+        <v>2717</v>
       </c>
       <c r="E4" t="n">
-        <v>51.35</v>
+        <v>62.37</v>
       </c>
       <c r="F4" t="n">
-        <v>402</v>
+        <v>485</v>
       </c>
       <c r="G4" t="n">
         <v>25</v>
@@ -955,10 +944,10 @@
         <v>0.57</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -967,34 +956,34 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>714</v>
+        <v>810</v>
       </c>
       <c r="N4" t="n">
-        <v>16.39</v>
+        <v>18.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3202</v>
       </c>
       <c r="P4" t="n">
-        <v>2639</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>60.58</v>
+        <v>957</v>
       </c>
       <c r="R4" t="n">
-        <v>1605</v>
+        <v>4368</v>
       </c>
       <c r="S4" t="n">
-        <v>3789</v>
+        <v>399</v>
       </c>
       <c r="T4" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="U4" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="V4" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1003,34 +992,34 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="Z4" t="n">
-        <v>543</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>6487</v>
       </c>
       <c r="AB4" t="n">
-        <v>6241</v>
+        <v>5430</v>
       </c>
       <c r="AC4" t="n">
-        <v>4550</v>
+        <v>959</v>
       </c>
       <c r="AD4" t="n">
-        <v>1605</v>
+        <v>4368</v>
       </c>
       <c r="AE4" t="n">
-        <v>3789</v>
+        <v>399</v>
       </c>
       <c r="AF4" t="n">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1039,31 +1028,28 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>588</v>
       </c>
       <c r="AL4" t="n">
-        <v>543</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>6487</v>
       </c>
       <c r="AN4" t="n">
-        <v>6240</v>
+        <v>5430</v>
       </c>
       <c r="AO4" t="n">
-        <v>4550</v>
+        <v>-2131</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1885</v>
+        <v>-2228</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1911</v>
+        <v>-2131</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1884</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-1911</v>
+        <v>-2228</v>
       </c>
     </row>
     <row r="5">
@@ -1081,19 +1067,19 @@
         <v>2096</v>
       </c>
       <c r="D5" t="n">
-        <v>1235</v>
+        <v>1529</v>
       </c>
       <c r="E5" t="n">
-        <v>58.92</v>
+        <v>72.95</v>
       </c>
       <c r="F5" t="n">
-        <v>260</v>
+        <v>328</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H5" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1108,103 +1094,100 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="N5" t="n">
-        <v>11.4</v>
+        <v>14.79</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1857</v>
       </c>
       <c r="P5" t="n">
-        <v>1495</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>71.33</v>
+        <v>382</v>
       </c>
       <c r="R5" t="n">
-        <v>805</v>
+        <v>2276</v>
       </c>
       <c r="S5" t="n">
-        <v>1886</v>
+        <v>121</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22</v>
+      </c>
+      <c r="W5" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>13</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="Z5" t="n">
-        <v>440</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>3306</v>
       </c>
       <c r="AB5" t="n">
-        <v>3158</v>
+        <v>2924</v>
       </c>
       <c r="AC5" t="n">
-        <v>2353</v>
+        <v>383</v>
       </c>
       <c r="AD5" t="n">
-        <v>806</v>
+        <v>2276</v>
       </c>
       <c r="AE5" t="n">
-        <v>1886</v>
+        <v>120</v>
       </c>
       <c r="AF5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="AL5" t="n">
-        <v>440</v>
+        <v>4</v>
       </c>
       <c r="AM5" t="n">
-        <v>8</v>
+        <v>3306</v>
       </c>
       <c r="AN5" t="n">
-        <v>3158</v>
+        <v>2923</v>
       </c>
       <c r="AO5" t="n">
-        <v>2352</v>
+        <v>-1210</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1062</v>
+        <v>-1067</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-858</v>
+        <v>-1210</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1062</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-857</v>
+        <v>-1066</v>
       </c>
     </row>
     <row r="6">
@@ -1222,19 +1205,19 @@
         <v>861</v>
       </c>
       <c r="D6" t="n">
-        <v>414</v>
+        <v>511</v>
       </c>
       <c r="E6" t="n">
-        <v>48.08</v>
+        <v>59.35</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>0.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1249,103 +1232,100 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N6" t="n">
-        <v>8.83</v>
+        <v>9.18</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="P6" t="n">
-        <v>473</v>
+        <v>67.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>54.94</v>
+        <v>310</v>
       </c>
       <c r="R6" t="n">
-        <v>421</v>
+        <v>694</v>
       </c>
       <c r="S6" t="n">
-        <v>558</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>113</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>832</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>310</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>694</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>93</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1134</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>693</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>422</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>558</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>31</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="AL6" t="n">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="AM6" t="n">
-        <v>8</v>
+        <v>1158</v>
       </c>
       <c r="AN6" t="n">
-        <v>1134</v>
+        <v>832</v>
       </c>
       <c r="AO6" t="n">
-        <v>692</v>
+        <v>-297</v>
       </c>
       <c r="AP6" t="n">
-        <v>-273</v>
+        <v>-247</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-220</v>
+        <v>-297</v>
       </c>
       <c r="AR6" t="n">
-        <v>-273</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-219</v>
+        <v>-247</v>
       </c>
     </row>
     <row r="7">
@@ -1363,13 +1343,13 @@
         <v>716</v>
       </c>
       <c r="D7" t="n">
-        <v>329</v>
+        <v>422</v>
       </c>
       <c r="E7" t="n">
-        <v>45.95</v>
+        <v>58.94</v>
       </c>
       <c r="F7" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
@@ -1390,103 +1370,100 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="N7" t="n">
-        <v>8.800000000000001</v>
+        <v>11.03</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="P7" t="n">
-        <v>415</v>
+        <v>75.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>57.96</v>
+        <v>280</v>
       </c>
       <c r="R7" t="n">
-        <v>384</v>
+        <v>644</v>
       </c>
       <c r="S7" t="n">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
         <v>1</v>
       </c>
-      <c r="V7" t="n">
-        <v>3</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>133</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1065</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>784</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>280</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>644</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>112</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1019</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>634</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>384</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>504</v>
-      </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1</v>
       </c>
-      <c r="AH7" t="n">
-        <v>3</v>
-      </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="AL7" t="n">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="AM7" t="n">
-        <v>4</v>
+        <v>1065</v>
       </c>
       <c r="AN7" t="n">
-        <v>1019</v>
+        <v>784</v>
       </c>
       <c r="AO7" t="n">
-        <v>634</v>
+        <v>-349</v>
       </c>
       <c r="AP7" t="n">
-        <v>-303</v>
+        <v>-246</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-219</v>
+        <v>-349</v>
       </c>
       <c r="AR7" t="n">
-        <v>-303</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-219</v>
+        <v>-246</v>
       </c>
     </row>
     <row r="8">
@@ -1504,19 +1481,19 @@
         <v>3369</v>
       </c>
       <c r="D8" t="n">
-        <v>1239</v>
+        <v>1594</v>
       </c>
       <c r="E8" t="n">
-        <v>36.78</v>
+        <v>47.31</v>
       </c>
       <c r="F8" t="n">
-        <v>308</v>
+        <v>435</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1531,103 +1508,100 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="N8" t="n">
-        <v>9.970000000000001</v>
+        <v>11.61</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2029</v>
       </c>
       <c r="P8" t="n">
-        <v>1547</v>
+        <v>60.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.92</v>
+        <v>1630</v>
       </c>
       <c r="R8" t="n">
-        <v>2049</v>
+        <v>2443</v>
       </c>
       <c r="S8" t="n">
-        <v>1986</v>
+        <v>289</v>
       </c>
       <c r="T8" t="n">
-        <v>223</v>
+        <v>27</v>
       </c>
       <c r="U8" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="X8" t="n">
         <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>378</v>
       </c>
       <c r="Z8" t="n">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>4810</v>
       </c>
       <c r="AB8" t="n">
-        <v>4596</v>
+        <v>3153</v>
       </c>
       <c r="AC8" t="n">
-        <v>2510</v>
+        <v>1630</v>
       </c>
       <c r="AD8" t="n">
-        <v>2049</v>
+        <v>2443</v>
       </c>
       <c r="AE8" t="n">
-        <v>1990</v>
+        <v>289</v>
       </c>
       <c r="AF8" t="n">
-        <v>220</v>
+        <v>27</v>
       </c>
       <c r="AG8" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
         <v>2</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>378</v>
       </c>
       <c r="AL8" t="n">
-        <v>277</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="n">
-        <v>9</v>
+        <v>4810</v>
       </c>
       <c r="AN8" t="n">
-        <v>4596</v>
+        <v>3153</v>
       </c>
       <c r="AO8" t="n">
-        <v>2510</v>
+        <v>-1441</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1227</v>
+        <v>-1124</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-963</v>
+        <v>-1441</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1227</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-963</v>
+        <v>-1124</v>
       </c>
     </row>
     <row r="9">
@@ -1645,19 +1619,19 @@
         <v>4381</v>
       </c>
       <c r="D9" t="n">
-        <v>1696</v>
+        <v>2466</v>
       </c>
       <c r="E9" t="n">
-        <v>38.71</v>
+        <v>56.29</v>
       </c>
       <c r="F9" t="n">
-        <v>405</v>
+        <v>611</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>0.41</v>
+        <v>0.66</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1672,103 +1646,100 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>317</v>
+        <v>391</v>
       </c>
       <c r="N9" t="n">
-        <v>7.24</v>
+        <v>8.92</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3077</v>
       </c>
       <c r="P9" t="n">
-        <v>2101</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.96</v>
+        <v>1980</v>
       </c>
       <c r="R9" t="n">
-        <v>2813</v>
+        <v>3260</v>
       </c>
       <c r="S9" t="n">
-        <v>2427</v>
+        <v>296</v>
       </c>
       <c r="T9" t="n">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="U9" t="n">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="V9" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="Z9" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>6348</v>
       </c>
       <c r="AB9" t="n">
-        <v>5997</v>
+        <v>4331</v>
       </c>
       <c r="AC9" t="n">
-        <v>3149</v>
+        <v>1980</v>
       </c>
       <c r="AD9" t="n">
-        <v>2808</v>
+        <v>3260</v>
       </c>
       <c r="AE9" t="n">
-        <v>2424</v>
+        <v>295</v>
       </c>
       <c r="AF9" t="n">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="AG9" t="n">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="AH9" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="AL9" t="n">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>6347</v>
       </c>
       <c r="AN9" t="n">
-        <v>5997</v>
+        <v>4330</v>
       </c>
       <c r="AO9" t="n">
-        <v>3152</v>
+        <v>-1967</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1616</v>
+        <v>-1254</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1048</v>
+        <v>-1966</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1616</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-1051</v>
+        <v>-1253</v>
       </c>
     </row>
     <row r="10">
@@ -1786,25 +1757,25 @@
         <v>5550</v>
       </c>
       <c r="D10" t="n">
-        <v>2064</v>
+        <v>2703</v>
       </c>
       <c r="E10" t="n">
-        <v>37.19</v>
+        <v>48.7</v>
       </c>
       <c r="F10" t="n">
-        <v>517</v>
+        <v>661</v>
       </c>
       <c r="G10" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1813,103 +1784,100 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>863</v>
+        <v>1030</v>
       </c>
       <c r="N10" t="n">
-        <v>15.55</v>
+        <v>18.56</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3364</v>
       </c>
       <c r="P10" t="n">
-        <v>2581</v>
+        <v>60.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>46.5</v>
+        <v>2620</v>
       </c>
       <c r="R10" t="n">
-        <v>3560</v>
+        <v>5034</v>
       </c>
       <c r="S10" t="n">
-        <v>3868</v>
+        <v>48</v>
       </c>
       <c r="T10" t="n">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="U10" t="n">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>542</v>
+      </c>
+      <c r="Z10" t="n">
         <v>6</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>456</v>
-      </c>
       <c r="AA10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5652</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2620</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5034</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>176</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>5</v>
       </c>
-      <c r="AB10" t="n">
-        <v>8064</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4368</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3560</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3868</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>136</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>542</v>
+      </c>
+      <c r="AL10" t="n">
         <v>6</v>
       </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>456</v>
-      </c>
       <c r="AM10" t="n">
-        <v>5</v>
+        <v>8448</v>
       </c>
       <c r="AN10" t="n">
-        <v>8064</v>
+        <v>5652</v>
       </c>
       <c r="AO10" t="n">
-        <v>4368</v>
+        <v>-2900</v>
       </c>
       <c r="AP10" t="n">
-        <v>-2514</v>
+        <v>-2288</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1787</v>
+        <v>-2898</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2514</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-1787</v>
+        <v>-2288</v>
       </c>
     </row>
     <row r="11">
@@ -1927,19 +1895,19 @@
         <v>4040</v>
       </c>
       <c r="D11" t="n">
-        <v>1669</v>
+        <v>2181</v>
       </c>
       <c r="E11" t="n">
-        <v>41.31</v>
+        <v>53.99</v>
       </c>
       <c r="F11" t="n">
-        <v>300</v>
+        <v>443</v>
       </c>
       <c r="G11" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H11" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1954,103 +1922,100 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>581</v>
+        <v>671</v>
       </c>
       <c r="N11" t="n">
-        <v>14.38</v>
+        <v>16.61</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2624</v>
       </c>
       <c r="P11" t="n">
-        <v>1969</v>
+        <v>64.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>48.74</v>
+        <v>1416</v>
       </c>
       <c r="R11" t="n">
-        <v>2077</v>
+        <v>3241</v>
       </c>
       <c r="S11" t="n">
-        <v>2487</v>
+        <v>37</v>
       </c>
       <c r="T11" t="n">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="U11" t="n">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>453</v>
+      </c>
+      <c r="Z11" t="n">
         <v>5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>371</v>
-      </c>
       <c r="AA11" t="n">
-        <v>4</v>
+        <v>5361</v>
       </c>
       <c r="AB11" t="n">
-        <v>5177</v>
+        <v>3797</v>
       </c>
       <c r="AC11" t="n">
-        <v>2983</v>
+        <v>1418</v>
       </c>
       <c r="AD11" t="n">
-        <v>2077</v>
+        <v>3241</v>
       </c>
       <c r="AE11" t="n">
-        <v>2487</v>
+        <v>35</v>
       </c>
       <c r="AF11" t="n">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="n">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="AH11" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>453</v>
+      </c>
+      <c r="AL11" t="n">
         <v>5</v>
       </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>371</v>
-      </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>5361</v>
       </c>
       <c r="AN11" t="n">
-        <v>5177</v>
+        <v>3795</v>
       </c>
       <c r="AO11" t="n">
-        <v>2983</v>
+        <v>-1321</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1137</v>
+        <v>-1173</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1014</v>
+        <v>-1321</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1137</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-1014</v>
+        <v>-1171</v>
       </c>
     </row>
     <row r="12">
@@ -2068,19 +2033,19 @@
         <v>2040</v>
       </c>
       <c r="D12" t="n">
-        <v>811</v>
+        <v>1133</v>
       </c>
       <c r="E12" t="n">
-        <v>39.75</v>
+        <v>55.54</v>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2095,103 +2060,100 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>9.41</v>
+        <v>11.03</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1240</v>
       </c>
       <c r="P12" t="n">
-        <v>880</v>
+        <v>60.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>43.14</v>
+        <v>751</v>
       </c>
       <c r="R12" t="n">
-        <v>1115</v>
+        <v>1250</v>
       </c>
       <c r="S12" t="n">
-        <v>844</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="V12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="Z12" t="n">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="AA12" t="n">
-        <v>16</v>
+        <v>2445</v>
       </c>
       <c r="AB12" t="n">
-        <v>2406</v>
+        <v>1608</v>
       </c>
       <c r="AC12" t="n">
-        <v>1266</v>
+        <v>751</v>
       </c>
       <c r="AD12" t="n">
-        <v>1115</v>
+        <v>1248</v>
       </c>
       <c r="AE12" t="n">
-        <v>841</v>
+        <v>15</v>
       </c>
       <c r="AF12" t="n">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="AG12" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AH12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="AL12" t="n">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="AM12" t="n">
-        <v>16</v>
+        <v>2445</v>
       </c>
       <c r="AN12" t="n">
-        <v>2406</v>
+        <v>1608</v>
       </c>
       <c r="AO12" t="n">
-        <v>1266</v>
+        <v>-405</v>
       </c>
       <c r="AP12" t="n">
-        <v>-366</v>
+        <v>-368</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-386</v>
+        <v>-405</v>
       </c>
       <c r="AR12" t="n">
-        <v>-366</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-386</v>
+        <v>-368</v>
       </c>
     </row>
     <row r="13">
@@ -2209,25 +2171,25 @@
         <v>6235</v>
       </c>
       <c r="D13" t="n">
-        <v>3168</v>
+        <v>4253</v>
       </c>
       <c r="E13" t="n">
-        <v>50.81</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>820</v>
+        <v>1149</v>
       </c>
       <c r="G13" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="H13" t="n">
-        <v>0.63</v>
+        <v>0.95</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2236,103 +2198,100 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>634</v>
+        <v>808</v>
       </c>
       <c r="N13" t="n">
-        <v>10.17</v>
+        <v>12.96</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5402</v>
       </c>
       <c r="P13" t="n">
-        <v>3988</v>
+        <v>86.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>63.96</v>
+        <v>1393</v>
       </c>
       <c r="R13" t="n">
-        <v>2948</v>
+        <v>7134</v>
       </c>
       <c r="S13" t="n">
-        <v>5564</v>
+        <v>54</v>
       </c>
       <c r="T13" t="n">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="U13" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="V13" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
+        <v>13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>969</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>9735</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8195</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1394</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>7134</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>54</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>146</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1</v>
       </c>
-      <c r="X13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>719</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AI13" t="n">
         <v>13</v>
       </c>
-      <c r="AB13" t="n">
-        <v>9558</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6511</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2682</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>5561</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>112</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>97</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="AL13" t="n">
-        <v>719</v>
+        <v>14</v>
       </c>
       <c r="AM13" t="n">
-        <v>13</v>
+        <v>9735</v>
       </c>
       <c r="AN13" t="n">
-        <v>9203</v>
+        <v>8195</v>
       </c>
       <c r="AO13" t="n">
-        <v>6424</v>
+        <v>-3500</v>
       </c>
       <c r="AP13" t="n">
-        <v>-3323</v>
+        <v>-2793</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-2523</v>
+        <v>-3500</v>
       </c>
       <c r="AR13" t="n">
-        <v>-2968</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-2436</v>
+        <v>-2793</v>
       </c>
     </row>
     <row r="14">
@@ -2350,19 +2309,19 @@
         <v>876</v>
       </c>
       <c r="D14" t="n">
-        <v>563</v>
+        <v>723</v>
       </c>
       <c r="E14" t="n">
-        <v>64.27</v>
+        <v>82.53</v>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2377,28 +2336,28 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
-        <v>5.94</v>
+        <v>6.85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="P14" t="n">
-        <v>629</v>
+        <v>92.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>71.8</v>
+        <v>99</v>
       </c>
       <c r="R14" t="n">
-        <v>269</v>
+        <v>891</v>
       </c>
       <c r="S14" t="n">
-        <v>723</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2413,28 +2372,28 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="Z14" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1190</v>
       </c>
       <c r="AB14" t="n">
-        <v>1155</v>
+        <v>1091</v>
       </c>
       <c r="AC14" t="n">
-        <v>886</v>
+        <v>99</v>
       </c>
       <c r="AD14" t="n">
-        <v>269</v>
+        <v>891</v>
       </c>
       <c r="AE14" t="n">
-        <v>723</v>
+        <v>25</v>
       </c>
       <c r="AF14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2449,31 +2408,28 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1190</v>
       </c>
       <c r="AN14" t="n">
-        <v>1155</v>
+        <v>1091</v>
       </c>
       <c r="AO14" t="n">
-        <v>886</v>
+        <v>-314</v>
       </c>
       <c r="AP14" t="n">
         <v>-279</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-257</v>
+        <v>-314</v>
       </c>
       <c r="AR14" t="n">
         <v>-279</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-257</v>
       </c>
     </row>
     <row r="15">
@@ -2491,10 +2447,10 @@
         <v>411</v>
       </c>
       <c r="D15" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E15" t="n">
-        <v>35.52</v>
+        <v>36.74</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
@@ -2524,97 +2480,94 @@
         <v>10.22</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="P15" t="n">
-        <v>181</v>
+        <v>45.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>44.04</v>
+        <v>213</v>
       </c>
       <c r="R15" t="n">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="S15" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>626</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>404</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>213</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>375</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG15" t="n">
         <v>3</v>
       </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL15" t="n">
         <v>1</v>
       </c>
-      <c r="AB15" t="n">
-        <v>622</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>394</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>223</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>370</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>20</v>
-      </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>626</v>
       </c>
       <c r="AN15" t="n">
-        <v>622</v>
+        <v>404</v>
       </c>
       <c r="AO15" t="n">
-        <v>394</v>
+        <v>-215</v>
       </c>
       <c r="AP15" t="n">
-        <v>-211</v>
+        <v>-218</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-213</v>
+        <v>-215</v>
       </c>
       <c r="AR15" t="n">
-        <v>-211</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-213</v>
+        <v>-218</v>
       </c>
     </row>
     <row r="16">
@@ -2632,19 +2585,19 @@
         <v>2170</v>
       </c>
       <c r="D16" t="n">
-        <v>907</v>
+        <v>1187</v>
       </c>
       <c r="E16" t="n">
-        <v>41.8</v>
+        <v>54.7</v>
       </c>
       <c r="F16" t="n">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2659,103 +2612,100 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="N16" t="n">
-        <v>10.55</v>
+        <v>12.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1410</v>
       </c>
       <c r="P16" t="n">
-        <v>1067</v>
+        <v>64.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>49.17</v>
+        <v>815</v>
       </c>
       <c r="R16" t="n">
-        <v>1162</v>
+        <v>1522</v>
       </c>
       <c r="S16" t="n">
-        <v>1195</v>
+        <v>53</v>
       </c>
       <c r="T16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" t="n">
+        <v>24</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>492</v>
+      </c>
+      <c r="Z16" t="n">
         <v>3</v>
       </c>
-      <c r="V16" t="n">
-        <v>12</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
+        <v>2921</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2106</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>815</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1522</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI16" t="n">
         <v>8</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>407</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>492</v>
+      </c>
+      <c r="AL16" t="n">
         <v>3</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2805</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1640</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1163</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1195</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>407</v>
-      </c>
       <c r="AM16" t="n">
-        <v>3</v>
+        <v>2921</v>
       </c>
       <c r="AN16" t="n">
-        <v>2804</v>
+        <v>2106</v>
       </c>
       <c r="AO16" t="n">
-        <v>1638</v>
+        <v>-751</v>
       </c>
       <c r="AP16" t="n">
-        <v>-635</v>
+        <v>-696</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-573</v>
+        <v>-751</v>
       </c>
       <c r="AR16" t="n">
-        <v>-634</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>-571</v>
+        <v>-696</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,222 +429,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Prelist Awal</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ditemukan</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Keluarga Baru</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Persentase Meninggal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tidak Eligible</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Eligible</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,222 +417,222 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Prelist Awal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ditemukan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Keluarga Baru</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Persentase Meninggal</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tidak Eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Persentase Tidak Eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Persentase Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,226 +425,236 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR16"/>
+  <dimension ref="A1:AT16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Prelist Awal</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ditemukan</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Keluarga Baru</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Persentase Meninggal</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Tidak Eligible</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Eligible</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Nonrespon</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Persentase Nonrespon</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -653,19 +675,19 @@
         <v>3059</v>
       </c>
       <c r="D2" t="n">
-        <v>2156</v>
+        <v>2565</v>
       </c>
       <c r="E2" t="n">
-        <v>70.48</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>390</v>
+        <v>466</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -680,100 +702,106 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>408</v>
+        <v>456</v>
       </c>
       <c r="N2" t="n">
-        <v>13.34</v>
+        <v>14.91</v>
       </c>
       <c r="O2" t="n">
-        <v>2546</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>83.23</v>
+        <v>24.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>643</v>
+        <v>3031</v>
       </c>
       <c r="R2" t="n">
-        <v>2752</v>
+        <v>99.08</v>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="T2" t="n">
-        <v>55</v>
+        <v>3545</v>
       </c>
       <c r="U2" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="n">
         <v>3</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AA2" t="n">
+        <v>770</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4454</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4424</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3533</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>84</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL2" t="n">
         <v>3</v>
       </c>
-      <c r="Y2" t="n">
-        <v>730</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4258</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3560</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>643</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2754</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>730</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>24</v>
-      </c>
       <c r="AM2" t="n">
-        <v>4258</v>
+        <v>770</v>
       </c>
       <c r="AN2" t="n">
-        <v>3560</v>
+        <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1199</v>
+        <v>4453</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1014</v>
+        <v>4423</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1199</v>
+        <v>-1395</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1014</v>
+        <v>-1393</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-1394</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-1392</v>
       </c>
     </row>
     <row r="3">
@@ -791,127 +819,133 @@
         <v>1133</v>
       </c>
       <c r="D3" t="n">
-        <v>638</v>
+        <v>749</v>
       </c>
       <c r="E3" t="n">
-        <v>56.31</v>
+        <v>66.11</v>
       </c>
       <c r="F3" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>3.09</v>
       </c>
       <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>202</v>
+      </c>
+      <c r="N3" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>870</v>
+      </c>
+      <c r="R3" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>52</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="U3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V3" t="n">
+        <v>105</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>171</v>
-      </c>
-      <c r="N3" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="O3" t="n">
-        <v>746</v>
-      </c>
-      <c r="P3" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>184</v>
-      </c>
-      <c r="R3" t="n">
-        <v>857</v>
-      </c>
-      <c r="S3" t="n">
-        <v>8</v>
-      </c>
-      <c r="T3" t="n">
-        <v>199</v>
-      </c>
-      <c r="U3" t="n">
-        <v>22</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
+        <v>215</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1513</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1356</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>52</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>105</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
         <v>4</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AL3" t="n">
         <v>1</v>
       </c>
-      <c r="Y3" t="n">
-        <v>212</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1107</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>184</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>857</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>199</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>212</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3</v>
-      </c>
       <c r="AM3" t="n">
-        <v>1490</v>
+        <v>215</v>
       </c>
       <c r="AN3" t="n">
-        <v>1107</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-357</v>
+        <v>1513</v>
       </c>
       <c r="AP3" t="n">
-        <v>-361</v>
+        <v>1356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-357</v>
+        <v>-380</v>
       </c>
       <c r="AR3" t="n">
-        <v>-361</v>
+        <v>-486</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-380</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-486</v>
       </c>
     </row>
     <row r="4">
@@ -929,25 +963,25 @@
         <v>4356</v>
       </c>
       <c r="D4" t="n">
-        <v>2717</v>
+        <v>3257</v>
       </c>
       <c r="E4" t="n">
-        <v>62.37</v>
+        <v>74.77</v>
       </c>
       <c r="F4" t="n">
-        <v>485</v>
+        <v>660</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -956,100 +990,106 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>810</v>
+        <v>938</v>
       </c>
       <c r="N4" t="n">
-        <v>18.6</v>
+        <v>21.53</v>
       </c>
       <c r="O4" t="n">
-        <v>3202</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>73.51000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>957</v>
+        <v>3917</v>
       </c>
       <c r="R4" t="n">
-        <v>4368</v>
+        <v>89.92</v>
       </c>
       <c r="S4" t="n">
-        <v>399</v>
+        <v>112</v>
       </c>
       <c r="T4" t="n">
-        <v>100</v>
+        <v>5543</v>
       </c>
       <c r="U4" t="n">
-        <v>73</v>
+        <v>389</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>588</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6487</v>
+        <v>592</v>
       </c>
       <c r="AB4" t="n">
-        <v>5430</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>959</v>
+        <v>6795</v>
       </c>
       <c r="AD4" t="n">
-        <v>4368</v>
+        <v>6662</v>
       </c>
       <c r="AE4" t="n">
-        <v>399</v>
+        <v>113</v>
       </c>
       <c r="AF4" t="n">
-        <v>98</v>
+        <v>5543</v>
       </c>
       <c r="AG4" t="n">
-        <v>73</v>
+        <v>388</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>588</v>
+        <v>4</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>6487</v>
+        <v>592</v>
       </c>
       <c r="AN4" t="n">
-        <v>5430</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>-2131</v>
+        <v>6795</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2228</v>
+        <v>6661</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2131</v>
+        <v>-2439</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2228</v>
+        <v>-2745</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-2439</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-2744</v>
       </c>
     </row>
     <row r="5">
@@ -1067,13 +1107,13 @@
         <v>2096</v>
       </c>
       <c r="D5" t="n">
-        <v>1529</v>
+        <v>1735</v>
       </c>
       <c r="E5" t="n">
-        <v>72.95</v>
+        <v>82.78</v>
       </c>
       <c r="F5" t="n">
-        <v>328</v>
+        <v>389</v>
       </c>
       <c r="G5" t="n">
         <v>21</v>
@@ -1094,100 +1134,106 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="N5" t="n">
-        <v>14.79</v>
+        <v>16.13</v>
       </c>
       <c r="O5" t="n">
-        <v>1857</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>88.59999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>382</v>
+        <v>2124</v>
       </c>
       <c r="R5" t="n">
-        <v>2276</v>
+        <v>101.34</v>
       </c>
       <c r="S5" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3010</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>501</v>
+      </c>
+      <c r="AB5" t="n">
         <v>4</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>488</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
+        <v>3521</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3521</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3010</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>501</v>
+      </c>
+      <c r="AN5" t="n">
         <v>4</v>
       </c>
-      <c r="AA5" t="n">
-        <v>3306</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2924</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>383</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2276</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>488</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>3306</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2923</v>
-      </c>
       <c r="AO5" t="n">
-        <v>-1210</v>
+        <v>3521</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1067</v>
+        <v>3521</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1210</v>
+        <v>-1425</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1066</v>
+        <v>-1397</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-1425</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-1397</v>
       </c>
     </row>
     <row r="6">
@@ -1205,127 +1251,133 @@
         <v>861</v>
       </c>
       <c r="D6" t="n">
-        <v>511</v>
+        <v>665</v>
       </c>
       <c r="E6" t="n">
-        <v>59.35</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>95</v>
+      </c>
+      <c r="N6" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>756</v>
+      </c>
+      <c r="R6" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>102</v>
+      </c>
+      <c r="T6" t="n">
+        <v>952</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" t="n">
         <v>7</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>79</v>
-      </c>
-      <c r="N6" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="O6" t="n">
-        <v>585</v>
-      </c>
-      <c r="P6" t="n">
-        <v>67.94</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>310</v>
-      </c>
-      <c r="R6" t="n">
-        <v>694</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>9</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>119</v>
+      </c>
+      <c r="AB6" t="n">
         <v>7</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1158</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>832</v>
-      </c>
       <c r="AC6" t="n">
-        <v>310</v>
+        <v>1209</v>
       </c>
       <c r="AD6" t="n">
-        <v>694</v>
+        <v>1100</v>
       </c>
       <c r="AE6" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="AF6" t="n">
+        <v>952</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI6" t="n">
         <v>16</v>
       </c>
-      <c r="AG6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>119</v>
+      </c>
+      <c r="AN6" t="n">
         <v>7</v>
       </c>
-      <c r="AM6" t="n">
-        <v>1158</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>832</v>
-      </c>
       <c r="AO6" t="n">
-        <v>-297</v>
+        <v>1209</v>
       </c>
       <c r="AP6" t="n">
-        <v>-247</v>
+        <v>1100</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-297</v>
+        <v>-348</v>
       </c>
       <c r="AR6" t="n">
-        <v>-247</v>
+        <v>-344</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-348</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-344</v>
       </c>
     </row>
     <row r="7">
@@ -1343,25 +1395,25 @@
         <v>716</v>
       </c>
       <c r="D7" t="n">
-        <v>422</v>
+        <v>572</v>
       </c>
       <c r="E7" t="n">
-        <v>58.94</v>
+        <v>79.89</v>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1370,100 +1422,106 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="N7" t="n">
-        <v>11.03</v>
+        <v>13.97</v>
       </c>
       <c r="O7" t="n">
-        <v>538</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>75.14</v>
+        <v>7.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>280</v>
+        <v>712</v>
       </c>
       <c r="R7" t="n">
-        <v>644</v>
+        <v>99.44</v>
       </c>
       <c r="S7" t="n">
+        <v>47</v>
+      </c>
+      <c r="T7" t="n">
+        <v>912</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>151</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1133</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1086</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>47</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>912</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>133</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>151</v>
+      </c>
+      <c r="AN7" t="n">
         <v>5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1065</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>784</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>280</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>644</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>133</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1065</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>784</v>
-      </c>
       <c r="AO7" t="n">
-        <v>-349</v>
+        <v>1133</v>
       </c>
       <c r="AP7" t="n">
-        <v>-246</v>
+        <v>1086</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-349</v>
+        <v>-417</v>
       </c>
       <c r="AR7" t="n">
-        <v>-246</v>
+        <v>-374</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-417</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-374</v>
       </c>
     </row>
     <row r="8">
@@ -1481,19 +1539,19 @@
         <v>3369</v>
       </c>
       <c r="D8" t="n">
-        <v>1594</v>
+        <v>2214</v>
       </c>
       <c r="E8" t="n">
-        <v>47.31</v>
+        <v>65.72</v>
       </c>
       <c r="F8" t="n">
-        <v>435</v>
+        <v>596</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>0.59</v>
+        <v>0.74</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1508,100 +1566,106 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>391</v>
+        <v>499</v>
       </c>
       <c r="N8" t="n">
-        <v>11.61</v>
+        <v>14.81</v>
       </c>
       <c r="O8" t="n">
-        <v>2029</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>60.23</v>
+        <v>8.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>1630</v>
+        <v>2810</v>
       </c>
       <c r="R8" t="n">
-        <v>2443</v>
+        <v>83.41</v>
       </c>
       <c r="S8" t="n">
-        <v>289</v>
+        <v>745</v>
       </c>
       <c r="T8" t="n">
-        <v>27</v>
+        <v>3557</v>
       </c>
       <c r="U8" t="n">
-        <v>25</v>
+        <v>205</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="W8" t="n">
-        <v>6</v>
+        <v>228</v>
       </c>
       <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2</v>
       </c>
-      <c r="Y8" t="n">
-        <v>378</v>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
+        <v>385</v>
+      </c>
+      <c r="AB8" t="n">
         <v>10</v>
       </c>
-      <c r="AA8" t="n">
-        <v>4810</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3153</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1630</v>
+        <v>5199</v>
       </c>
       <c r="AD8" t="n">
-        <v>2443</v>
+        <v>4402</v>
       </c>
       <c r="AE8" t="n">
-        <v>289</v>
+        <v>748</v>
       </c>
       <c r="AF8" t="n">
-        <v>27</v>
+        <v>3555</v>
       </c>
       <c r="AG8" t="n">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>228</v>
       </c>
       <c r="AJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL8" t="n">
         <v>2</v>
       </c>
-      <c r="AK8" t="n">
-        <v>378</v>
-      </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
+        <v>385</v>
+      </c>
+      <c r="AN8" t="n">
         <v>10</v>
       </c>
-      <c r="AM8" t="n">
-        <v>4810</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>3153</v>
-      </c>
       <c r="AO8" t="n">
-        <v>-1441</v>
+        <v>5199</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1124</v>
+        <v>4399</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1441</v>
+        <v>-1830</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1124</v>
+        <v>-1592</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-1830</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-1589</v>
       </c>
     </row>
     <row r="9">
@@ -1619,19 +1683,19 @@
         <v>4381</v>
       </c>
       <c r="D9" t="n">
-        <v>2466</v>
+        <v>3194</v>
       </c>
       <c r="E9" t="n">
-        <v>56.29</v>
+        <v>72.91</v>
       </c>
       <c r="F9" t="n">
-        <v>611</v>
+        <v>743</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1646,100 +1710,106 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="N9" t="n">
-        <v>8.92</v>
+        <v>10.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3077</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>70.23999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>1980</v>
+        <v>3937</v>
       </c>
       <c r="R9" t="n">
-        <v>3260</v>
+        <v>89.87</v>
       </c>
       <c r="S9" t="n">
-        <v>296</v>
+        <v>742</v>
       </c>
       <c r="T9" t="n">
-        <v>37</v>
+        <v>4117</v>
       </c>
       <c r="U9" t="n">
-        <v>198</v>
+        <v>780</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Y9" t="n">
-        <v>577</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>6348</v>
+        <v>625</v>
       </c>
       <c r="AB9" t="n">
-        <v>4331</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1980</v>
+        <v>6749</v>
       </c>
       <c r="AD9" t="n">
-        <v>3260</v>
+        <v>5894</v>
       </c>
       <c r="AE9" t="n">
-        <v>295</v>
+        <v>742</v>
       </c>
       <c r="AF9" t="n">
-        <v>37</v>
+        <v>4117</v>
       </c>
       <c r="AG9" t="n">
-        <v>198</v>
+        <v>780</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AK9" t="n">
-        <v>577</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>6347</v>
+        <v>625</v>
       </c>
       <c r="AN9" t="n">
-        <v>4330</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1967</v>
+        <v>6749</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1254</v>
+        <v>5894</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1966</v>
+        <v>-2368</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1253</v>
+        <v>-1957</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-2368</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>-1957</v>
       </c>
     </row>
     <row r="10">
@@ -1757,127 +1827,133 @@
         <v>5550</v>
       </c>
       <c r="D10" t="n">
-        <v>2703</v>
+        <v>3498</v>
       </c>
       <c r="E10" t="n">
-        <v>48.7</v>
+        <v>63.03</v>
       </c>
       <c r="F10" t="n">
-        <v>661</v>
+        <v>815</v>
       </c>
       <c r="G10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H10" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="I10" t="n">
+        <v>11</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1306</v>
+      </c>
+      <c r="N10" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="O10" t="n">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1030</v>
-      </c>
-      <c r="N10" t="n">
-        <v>18.56</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3364</v>
-      </c>
       <c r="P10" t="n">
-        <v>60.61</v>
+        <v>20.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>2620</v>
+        <v>4313</v>
       </c>
       <c r="R10" t="n">
-        <v>5034</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="T10" t="n">
-        <v>178</v>
+        <v>6975</v>
       </c>
       <c r="U10" t="n">
-        <v>15</v>
+        <v>281</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="W10" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="X10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2</v>
       </c>
-      <c r="Y10" t="n">
-        <v>542</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>6</v>
-      </c>
       <c r="AA10" t="n">
-        <v>8450</v>
+        <v>580</v>
       </c>
       <c r="AB10" t="n">
-        <v>5652</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2620</v>
+        <v>8991</v>
       </c>
       <c r="AD10" t="n">
-        <v>5034</v>
+        <v>7916</v>
       </c>
       <c r="AE10" t="n">
-        <v>48</v>
+        <v>981</v>
       </c>
       <c r="AF10" t="n">
-        <v>176</v>
+        <v>6975</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>280</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AI10" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL10" t="n">
         <v>2</v>
       </c>
-      <c r="AK10" t="n">
-        <v>542</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>6</v>
-      </c>
       <c r="AM10" t="n">
-        <v>8448</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>5652</v>
+        <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>-2900</v>
+        <v>8991</v>
       </c>
       <c r="AP10" t="n">
-        <v>-2288</v>
+        <v>7915</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-2898</v>
+        <v>-3441</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2288</v>
+        <v>-3603</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-3441</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-3602</v>
       </c>
     </row>
     <row r="11">
@@ -1895,25 +1971,25 @@
         <v>4040</v>
       </c>
       <c r="D11" t="n">
-        <v>2181</v>
+        <v>2717</v>
       </c>
       <c r="E11" t="n">
-        <v>53.99</v>
+        <v>67.25</v>
       </c>
       <c r="F11" t="n">
-        <v>443</v>
+        <v>596</v>
       </c>
       <c r="G11" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H11" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1922,100 +1998,106 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>671</v>
+        <v>904</v>
       </c>
       <c r="N11" t="n">
-        <v>16.61</v>
+        <v>22.38</v>
       </c>
       <c r="O11" t="n">
-        <v>2624</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>64.95</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1416</v>
+        <v>3313</v>
       </c>
       <c r="R11" t="n">
-        <v>3241</v>
+        <v>82</v>
       </c>
       <c r="S11" t="n">
-        <v>37</v>
+        <v>432</v>
       </c>
       <c r="T11" t="n">
-        <v>148</v>
+        <v>4389</v>
       </c>
       <c r="U11" t="n">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="W11" t="n">
+        <v>17</v>
+      </c>
+      <c r="X11" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y11" t="n">
         <v>6</v>
       </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>453</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
-        <v>5361</v>
+        <v>468</v>
       </c>
       <c r="AB11" t="n">
-        <v>3797</v>
+        <v>6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1418</v>
+        <v>5634</v>
       </c>
       <c r="AD11" t="n">
-        <v>3241</v>
+        <v>5057</v>
       </c>
       <c r="AE11" t="n">
-        <v>35</v>
+        <v>434</v>
       </c>
       <c r="AF11" t="n">
-        <v>148</v>
+        <v>4389</v>
       </c>
       <c r="AG11" t="n">
-        <v>55</v>
+        <v>149</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="AI11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK11" t="n">
         <v>6</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>453</v>
-      </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>5361</v>
+        <v>468</v>
       </c>
       <c r="AN11" t="n">
-        <v>3795</v>
+        <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1321</v>
+        <v>5634</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1173</v>
+        <v>5055</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1321</v>
+        <v>-1594</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1171</v>
+        <v>-1744</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-1594</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-1742</v>
       </c>
     </row>
     <row r="12">
@@ -2033,19 +2115,19 @@
         <v>2040</v>
       </c>
       <c r="D12" t="n">
-        <v>1133</v>
+        <v>1563</v>
       </c>
       <c r="E12" t="n">
-        <v>55.54</v>
+        <v>76.62</v>
       </c>
       <c r="F12" t="n">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2060,100 +2142,106 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="N12" t="n">
-        <v>11.03</v>
+        <v>13.04</v>
       </c>
       <c r="O12" t="n">
-        <v>1240</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>60.78</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>751</v>
+        <v>1700</v>
       </c>
       <c r="R12" t="n">
-        <v>1250</v>
+        <v>83.33</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="T12" t="n">
-        <v>86</v>
+        <v>1652</v>
       </c>
       <c r="U12" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="W12" t="n">
+        <v>134</v>
+      </c>
+      <c r="X12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y12" t="n">
         <v>7</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>1</v>
       </c>
-      <c r="Y12" t="n">
-        <v>249</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>18</v>
-      </c>
       <c r="AA12" t="n">
-        <v>2445</v>
+        <v>258</v>
       </c>
       <c r="AB12" t="n">
-        <v>1608</v>
+        <v>19</v>
       </c>
       <c r="AC12" t="n">
-        <v>751</v>
+        <v>2485</v>
       </c>
       <c r="AD12" t="n">
-        <v>1248</v>
+        <v>2257</v>
       </c>
       <c r="AE12" t="n">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="AF12" t="n">
-        <v>86</v>
+        <v>1652</v>
       </c>
       <c r="AG12" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AI12" t="n">
+        <v>134</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK12" t="n">
         <v>7</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AL12" t="n">
         <v>1</v>
       </c>
-      <c r="AK12" t="n">
-        <v>249</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>18</v>
-      </c>
       <c r="AM12" t="n">
-        <v>2445</v>
+        <v>258</v>
       </c>
       <c r="AN12" t="n">
-        <v>1608</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="n">
-        <v>-405</v>
+        <v>2485</v>
       </c>
       <c r="AP12" t="n">
-        <v>-368</v>
+        <v>2257</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-405</v>
+        <v>-445</v>
       </c>
       <c r="AR12" t="n">
-        <v>-368</v>
+        <v>-557</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-445</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-557</v>
       </c>
     </row>
     <row r="13">
@@ -2171,19 +2259,19 @@
         <v>6235</v>
       </c>
       <c r="D13" t="n">
-        <v>4253</v>
+        <v>5075</v>
       </c>
       <c r="E13" t="n">
-        <v>68.20999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1149</v>
+        <v>1391</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H13" t="n">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
@@ -2198,100 +2286,106 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>808</v>
+        <v>980</v>
       </c>
       <c r="N13" t="n">
-        <v>12.96</v>
+        <v>15.72</v>
       </c>
       <c r="O13" t="n">
-        <v>5402</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>86.64</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1393</v>
+        <v>6466</v>
       </c>
       <c r="R13" t="n">
-        <v>7134</v>
+        <v>103.7</v>
       </c>
       <c r="S13" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="T13" t="n">
-        <v>147</v>
+        <v>8976</v>
       </c>
       <c r="U13" t="n">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="W13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>969</v>
+        <v>44</v>
       </c>
       <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>983</v>
+      </c>
+      <c r="AB13" t="n">
         <v>14</v>
       </c>
-      <c r="AA13" t="n">
-        <v>9735</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>8195</v>
-      </c>
       <c r="AC13" t="n">
-        <v>1394</v>
+        <v>10379</v>
       </c>
       <c r="AD13" t="n">
-        <v>7134</v>
+        <v>10172</v>
       </c>
       <c r="AE13" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="AF13" t="n">
-        <v>146</v>
+        <v>8976</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="AI13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>969</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>983</v>
+      </c>
+      <c r="AN13" t="n">
         <v>14</v>
       </c>
-      <c r="AM13" t="n">
-        <v>9735</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8195</v>
-      </c>
       <c r="AO13" t="n">
-        <v>-3500</v>
+        <v>10379</v>
       </c>
       <c r="AP13" t="n">
-        <v>-2793</v>
+        <v>10171</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-3500</v>
+        <v>-4144</v>
       </c>
       <c r="AR13" t="n">
-        <v>-2793</v>
+        <v>-3706</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-4144</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-3705</v>
       </c>
     </row>
     <row r="14">
@@ -2309,19 +2403,19 @@
         <v>876</v>
       </c>
       <c r="D14" t="n">
-        <v>723</v>
+        <v>801</v>
       </c>
       <c r="E14" t="n">
-        <v>82.53</v>
+        <v>91.44</v>
       </c>
       <c r="F14" t="n">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2336,28 +2430,28 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N14" t="n">
-        <v>6.85</v>
+        <v>7.76</v>
       </c>
       <c r="O14" t="n">
-        <v>812</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>92.69</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>99</v>
+        <v>908</v>
       </c>
       <c r="R14" t="n">
-        <v>891</v>
+        <v>103.65</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1038</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2372,28 +2466,28 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>175</v>
       </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1190</v>
-      </c>
       <c r="AB14" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>99</v>
+        <v>1215</v>
       </c>
       <c r="AD14" t="n">
-        <v>891</v>
+        <v>1215</v>
       </c>
       <c r="AE14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1038</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2408,28 +2502,34 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
         <v>175</v>
       </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1190</v>
-      </c>
       <c r="AN14" t="n">
-        <v>1091</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-314</v>
+        <v>1215</v>
       </c>
       <c r="AP14" t="n">
-        <v>-279</v>
+        <v>1215</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-314</v>
+        <v>-339</v>
       </c>
       <c r="AR14" t="n">
-        <v>-279</v>
+        <v>-307</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-339</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-307</v>
       </c>
     </row>
     <row r="15">
@@ -2447,26 +2547,26 @@
         <v>411</v>
       </c>
       <c r="D15" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E15" t="n">
-        <v>36.74</v>
+        <v>39.42</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
       </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.24</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
@@ -2474,100 +2574,106 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N15" t="n">
-        <v>10.22</v>
+        <v>9.98</v>
       </c>
       <c r="O15" t="n">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="P15" t="n">
-        <v>45.26</v>
+        <v>78.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="R15" t="n">
-        <v>375</v>
+        <v>47.93</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="T15" t="n">
-        <v>9</v>
+        <v>408</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
         <v>25</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>1</v>
       </c>
-      <c r="AA15" t="n">
-        <v>626</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>404</v>
-      </c>
       <c r="AC15" t="n">
-        <v>213</v>
+        <v>636</v>
       </c>
       <c r="AD15" t="n">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="AF15" t="n">
-        <v>9</v>
+        <v>408</v>
       </c>
       <c r="AG15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
         <v>25</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AN15" t="n">
         <v>1</v>
       </c>
-      <c r="AM15" t="n">
-        <v>626</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>404</v>
-      </c>
       <c r="AO15" t="n">
-        <v>-215</v>
+        <v>636</v>
       </c>
       <c r="AP15" t="n">
-        <v>-218</v>
+        <v>435</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-215</v>
+        <v>-225</v>
       </c>
       <c r="AR15" t="n">
-        <v>-218</v>
+        <v>-238</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-225</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-238</v>
       </c>
     </row>
     <row r="16">
@@ -2585,19 +2691,19 @@
         <v>2170</v>
       </c>
       <c r="D16" t="n">
-        <v>1187</v>
+        <v>1618</v>
       </c>
       <c r="E16" t="n">
-        <v>54.7</v>
+        <v>74.56</v>
       </c>
       <c r="F16" t="n">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H16" t="n">
-        <v>0.92</v>
+        <v>1.06</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2612,100 +2718,106 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>268</v>
+        <v>317</v>
       </c>
       <c r="N16" t="n">
-        <v>12.35</v>
+        <v>14.61</v>
       </c>
       <c r="O16" t="n">
-        <v>1410</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>64.98</v>
+        <v>3.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>815</v>
+        <v>1898</v>
       </c>
       <c r="R16" t="n">
-        <v>1522</v>
+        <v>87.47</v>
       </c>
       <c r="S16" t="n">
-        <v>53</v>
+        <v>275</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2176</v>
       </c>
       <c r="U16" t="n">
+        <v>11</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>10</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>516</v>
+      </c>
+      <c r="AB16" t="n">
         <v>4</v>
       </c>
-      <c r="V16" t="n">
-        <v>24</v>
-      </c>
-      <c r="W16" t="n">
-        <v>8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>492</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2921</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2106</v>
-      </c>
       <c r="AC16" t="n">
-        <v>815</v>
+        <v>3009</v>
       </c>
       <c r="AD16" t="n">
-        <v>1522</v>
+        <v>2734</v>
       </c>
       <c r="AE16" t="n">
-        <v>53</v>
+        <v>276</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2176</v>
       </c>
       <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>516</v>
+      </c>
+      <c r="AN16" t="n">
         <v>4</v>
       </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>492</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>2921</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2106</v>
-      </c>
       <c r="AO16" t="n">
-        <v>-751</v>
+        <v>3009</v>
       </c>
       <c r="AP16" t="n">
-        <v>-696</v>
+        <v>2733</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-751</v>
+        <v>-839</v>
       </c>
       <c r="AR16" t="n">
-        <v>-696</v>
+        <v>-836</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-839</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-835</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,236 +413,226 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT16"/>
+  <dimension ref="A1:AR16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Prelist Awal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Ditemukan</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Ditemukan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Keluarga Baru</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Meninggal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Persentase Meninggal</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tidak Eligible</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Persentase Tidak Eligible</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Persentase Tidak Dapat Ditemui Sampai Akhir Pendataan</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Persentase Tidak Ditemukan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Nonrespon</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Persentase Nonrespon</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Persentase Total Hasil Pendataan ((4) + (5))</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Diff_Target_Pencacah</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pencacah</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Diff_Target_Pengawas</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Diff_Realisasi_Pengawas</t>
         </is>
@@ -675,19 +653,19 @@
         <v>3059</v>
       </c>
       <c r="D2" t="n">
-        <v>2565</v>
+        <v>2156</v>
       </c>
       <c r="E2" t="n">
-        <v>83.84999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="F2" t="n">
-        <v>466</v>
+        <v>390</v>
       </c>
       <c r="G2" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -702,106 +680,100 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="N2" t="n">
-        <v>14.91</v>
+        <v>13.34</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>2546</v>
       </c>
       <c r="P2" t="n">
-        <v>24.29</v>
+        <v>83.23</v>
       </c>
       <c r="Q2" t="n">
-        <v>3031</v>
+        <v>643</v>
       </c>
       <c r="R2" t="n">
-        <v>99.08</v>
+        <v>2752</v>
       </c>
       <c r="S2" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="T2" t="n">
-        <v>3545</v>
+        <v>55</v>
       </c>
       <c r="U2" t="n">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
+        <v>730</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4258</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3560</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>643</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2754</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
         <v>5</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>3</v>
       </c>
-      <c r="AA2" t="n">
-        <v>770</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4454</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4424</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>3533</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>84</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1</v>
-      </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>730</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="AM2" t="n">
-        <v>770</v>
+        <v>4258</v>
       </c>
       <c r="AN2" t="n">
-        <v>27</v>
+        <v>3560</v>
       </c>
       <c r="AO2" t="n">
-        <v>4453</v>
+        <v>-1199</v>
       </c>
       <c r="AP2" t="n">
-        <v>4423</v>
+        <v>-1014</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1395</v>
+        <v>-1199</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1393</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-1394</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-1392</v>
+        <v>-1014</v>
       </c>
     </row>
     <row r="3">
@@ -819,25 +791,25 @@
         <v>1133</v>
       </c>
       <c r="D3" t="n">
-        <v>749</v>
+        <v>638</v>
       </c>
       <c r="E3" t="n">
-        <v>66.11</v>
+        <v>56.31</v>
       </c>
       <c r="F3" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>3.09</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -846,106 +818,100 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="N3" t="n">
-        <v>17.83</v>
+        <v>15.09</v>
       </c>
       <c r="O3" t="n">
+        <v>746</v>
+      </c>
+      <c r="P3" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>184</v>
+      </c>
+      <c r="R3" t="n">
+        <v>857</v>
+      </c>
+      <c r="S3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" t="n">
+        <v>199</v>
+      </c>
+      <c r="U3" t="n">
+        <v>22</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
         <v>4</v>
       </c>
-      <c r="P3" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>870</v>
-      </c>
-      <c r="R3" t="n">
-        <v>76.79000000000001</v>
-      </c>
-      <c r="S3" t="n">
-        <v>52</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1112</v>
-      </c>
-      <c r="U3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V3" t="n">
-        <v>105</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
+        <v>212</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1490</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1107</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>184</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>857</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>199</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>4</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AJ3" t="n">
         <v>1</v>
       </c>
-      <c r="AA3" t="n">
-        <v>215</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1513</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1356</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>52</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1112</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>105</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>212</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
-        <v>215</v>
+        <v>1490</v>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>1107</v>
       </c>
       <c r="AO3" t="n">
-        <v>1513</v>
+        <v>-357</v>
       </c>
       <c r="AP3" t="n">
-        <v>1356</v>
+        <v>-361</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-380</v>
+        <v>-357</v>
       </c>
       <c r="AR3" t="n">
-        <v>-486</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-380</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-486</v>
+        <v>-361</v>
       </c>
     </row>
     <row r="4">
@@ -963,25 +929,25 @@
         <v>4356</v>
       </c>
       <c r="D4" t="n">
-        <v>3257</v>
+        <v>2717</v>
       </c>
       <c r="E4" t="n">
-        <v>74.77</v>
+        <v>62.37</v>
       </c>
       <c r="F4" t="n">
-        <v>660</v>
+        <v>485</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -990,106 +956,100 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>938</v>
+        <v>810</v>
       </c>
       <c r="N4" t="n">
-        <v>21.53</v>
+        <v>18.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3202</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>3917</v>
+        <v>957</v>
       </c>
       <c r="R4" t="n">
-        <v>89.92</v>
+        <v>4368</v>
       </c>
       <c r="S4" t="n">
-        <v>112</v>
+        <v>399</v>
       </c>
       <c r="T4" t="n">
-        <v>5543</v>
+        <v>100</v>
       </c>
       <c r="U4" t="n">
-        <v>389</v>
+        <v>73</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>588</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>592</v>
+        <v>6487</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>5430</v>
       </c>
       <c r="AC4" t="n">
-        <v>6795</v>
+        <v>959</v>
       </c>
       <c r="AD4" t="n">
-        <v>6662</v>
+        <v>4368</v>
       </c>
       <c r="AE4" t="n">
-        <v>113</v>
+        <v>399</v>
       </c>
       <c r="AF4" t="n">
-        <v>5543</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="n">
-        <v>388</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>4</v>
+        <v>588</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
-        <v>592</v>
+        <v>6487</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>5430</v>
       </c>
       <c r="AO4" t="n">
-        <v>6795</v>
+        <v>-2131</v>
       </c>
       <c r="AP4" t="n">
-        <v>6661</v>
+        <v>-2228</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2439</v>
+        <v>-2131</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2745</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-2439</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-2744</v>
+        <v>-2228</v>
       </c>
     </row>
     <row r="5">
@@ -1107,13 +1067,13 @@
         <v>2096</v>
       </c>
       <c r="D5" t="n">
-        <v>1735</v>
+        <v>1529</v>
       </c>
       <c r="E5" t="n">
-        <v>82.78</v>
+        <v>72.95</v>
       </c>
       <c r="F5" t="n">
-        <v>389</v>
+        <v>328</v>
       </c>
       <c r="G5" t="n">
         <v>21</v>
@@ -1134,106 +1094,100 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="N5" t="n">
-        <v>16.13</v>
+        <v>14.79</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>1857</v>
       </c>
       <c r="P5" t="n">
-        <v>1.06</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>2124</v>
+        <v>382</v>
       </c>
       <c r="R5" t="n">
-        <v>101.34</v>
+        <v>2276</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="T5" t="n">
-        <v>3010</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>488</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>501</v>
+        <v>3306</v>
       </c>
       <c r="AB5" t="n">
+        <v>2924</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>383</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2276</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
         <v>4</v>
       </c>
-      <c r="AC5" t="n">
-        <v>3521</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3521</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3010</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>6</v>
+        <v>488</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM5" t="n">
-        <v>501</v>
+        <v>3306</v>
       </c>
       <c r="AN5" t="n">
-        <v>4</v>
+        <v>2923</v>
       </c>
       <c r="AO5" t="n">
-        <v>3521</v>
+        <v>-1210</v>
       </c>
       <c r="AP5" t="n">
-        <v>3521</v>
+        <v>-1067</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1425</v>
+        <v>-1210</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1397</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-1425</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-1397</v>
+        <v>-1066</v>
       </c>
     </row>
     <row r="6">
@@ -1251,19 +1205,19 @@
         <v>861</v>
       </c>
       <c r="D6" t="n">
-        <v>665</v>
+        <v>511</v>
       </c>
       <c r="E6" t="n">
-        <v>77.23999999999999</v>
+        <v>59.35</v>
       </c>
       <c r="F6" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1278,106 +1232,100 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="N6" t="n">
-        <v>11.03</v>
+        <v>9.18</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>67.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>756</v>
+        <v>310</v>
       </c>
       <c r="R6" t="n">
-        <v>87.8</v>
+        <v>694</v>
       </c>
       <c r="S6" t="n">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>952</v>
+        <v>16</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>113</v>
+      </c>
+      <c r="Z6" t="n">
         <v>7</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>832</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>310</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>694</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF6" t="n">
         <v>16</v>
       </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>119</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AG6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>113</v>
+      </c>
+      <c r="AL6" t="n">
         <v>7</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1209</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>102</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>952</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
       <c r="AM6" t="n">
-        <v>119</v>
+        <v>1158</v>
       </c>
       <c r="AN6" t="n">
-        <v>7</v>
+        <v>832</v>
       </c>
       <c r="AO6" t="n">
-        <v>1209</v>
+        <v>-297</v>
       </c>
       <c r="AP6" t="n">
-        <v>1100</v>
+        <v>-247</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-348</v>
+        <v>-297</v>
       </c>
       <c r="AR6" t="n">
-        <v>-344</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>-348</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>-344</v>
+        <v>-247</v>
       </c>
     </row>
     <row r="7">
@@ -1395,25 +1343,25 @@
         <v>716</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>422</v>
       </c>
       <c r="E7" t="n">
-        <v>79.89</v>
+        <v>58.94</v>
       </c>
       <c r="F7" t="n">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1422,106 +1370,100 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="N7" t="n">
-        <v>13.97</v>
+        <v>11.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>538</v>
       </c>
       <c r="P7" t="n">
-        <v>7.82</v>
+        <v>75.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>712</v>
+        <v>280</v>
       </c>
       <c r="R7" t="n">
-        <v>99.44</v>
+        <v>644</v>
       </c>
       <c r="S7" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>912</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>133</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1065</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>784</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>280</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>644</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>151</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>133</v>
+      </c>
+      <c r="AL7" t="n">
         <v>5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1133</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1086</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>47</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>912</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
       <c r="AM7" t="n">
-        <v>151</v>
+        <v>1065</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>784</v>
       </c>
       <c r="AO7" t="n">
-        <v>1133</v>
+        <v>-349</v>
       </c>
       <c r="AP7" t="n">
-        <v>1086</v>
+        <v>-246</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-417</v>
+        <v>-349</v>
       </c>
       <c r="AR7" t="n">
-        <v>-374</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-417</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>-374</v>
+        <v>-246</v>
       </c>
     </row>
     <row r="8">
@@ -1539,133 +1481,127 @@
         <v>3369</v>
       </c>
       <c r="D8" t="n">
-        <v>2214</v>
+        <v>1594</v>
       </c>
       <c r="E8" t="n">
-        <v>65.72</v>
+        <v>47.31</v>
       </c>
       <c r="F8" t="n">
-        <v>596</v>
+        <v>435</v>
       </c>
       <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>391</v>
+      </c>
+      <c r="N8" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2029</v>
+      </c>
+      <c r="P8" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1630</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2443</v>
+      </c>
+      <c r="S8" t="n">
+        <v>289</v>
+      </c>
+      <c r="T8" t="n">
+        <v>27</v>
+      </c>
+      <c r="U8" t="n">
         <v>25</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>499</v>
-      </c>
-      <c r="N8" t="n">
-        <v>14.81</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2810</v>
-      </c>
-      <c r="R8" t="n">
-        <v>83.41</v>
-      </c>
-      <c r="S8" t="n">
-        <v>745</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3557</v>
-      </c>
-      <c r="U8" t="n">
-        <v>205</v>
-      </c>
       <c r="V8" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>228</v>
+        <v>6</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>378</v>
       </c>
       <c r="Z8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4810</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3153</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1630</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2443</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>289</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2</v>
       </c>
-      <c r="AA8" t="n">
-        <v>385</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AK8" t="n">
+        <v>378</v>
+      </c>
+      <c r="AL8" t="n">
         <v>10</v>
       </c>
-      <c r="AC8" t="n">
-        <v>5199</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>4402</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>748</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>3555</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>204</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>52</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>228</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2</v>
-      </c>
       <c r="AM8" t="n">
-        <v>385</v>
+        <v>4810</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>3153</v>
       </c>
       <c r="AO8" t="n">
-        <v>5199</v>
+        <v>-1441</v>
       </c>
       <c r="AP8" t="n">
-        <v>4399</v>
+        <v>-1124</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-1830</v>
+        <v>-1441</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1592</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-1830</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-1589</v>
+        <v>-1124</v>
       </c>
     </row>
     <row r="9">
@@ -1683,19 +1619,19 @@
         <v>4381</v>
       </c>
       <c r="D9" t="n">
-        <v>3194</v>
+        <v>2466</v>
       </c>
       <c r="E9" t="n">
-        <v>72.91</v>
+        <v>56.29</v>
       </c>
       <c r="F9" t="n">
-        <v>743</v>
+        <v>611</v>
       </c>
       <c r="G9" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1710,106 +1646,100 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>473</v>
+        <v>391</v>
       </c>
       <c r="N9" t="n">
-        <v>10.8</v>
+        <v>8.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>3077</v>
       </c>
       <c r="P9" t="n">
-        <v>0.67</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>3937</v>
+        <v>1980</v>
       </c>
       <c r="R9" t="n">
-        <v>89.87</v>
+        <v>3260</v>
       </c>
       <c r="S9" t="n">
-        <v>742</v>
+        <v>296</v>
       </c>
       <c r="T9" t="n">
-        <v>4117</v>
+        <v>37</v>
       </c>
       <c r="U9" t="n">
-        <v>780</v>
+        <v>198</v>
       </c>
       <c r="V9" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>577</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>625</v>
+        <v>6348</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>4331</v>
       </c>
       <c r="AC9" t="n">
-        <v>6749</v>
+        <v>1980</v>
       </c>
       <c r="AD9" t="n">
-        <v>5894</v>
+        <v>3260</v>
       </c>
       <c r="AE9" t="n">
-        <v>742</v>
+        <v>295</v>
       </c>
       <c r="AF9" t="n">
-        <v>4117</v>
+        <v>37</v>
       </c>
       <c r="AG9" t="n">
-        <v>780</v>
+        <v>198</v>
       </c>
       <c r="AH9" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>577</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>625</v>
+        <v>6347</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>4330</v>
       </c>
       <c r="AO9" t="n">
-        <v>6749</v>
+        <v>-1967</v>
       </c>
       <c r="AP9" t="n">
-        <v>5894</v>
+        <v>-1254</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-2368</v>
+        <v>-1966</v>
       </c>
       <c r="AR9" t="n">
-        <v>-1957</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-2368</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-1957</v>
+        <v>-1253</v>
       </c>
     </row>
     <row r="10">
@@ -1827,25 +1757,25 @@
         <v>5550</v>
       </c>
       <c r="D10" t="n">
-        <v>3498</v>
+        <v>2703</v>
       </c>
       <c r="E10" t="n">
-        <v>63.03</v>
+        <v>48.7</v>
       </c>
       <c r="F10" t="n">
-        <v>815</v>
+        <v>661</v>
       </c>
       <c r="G10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H10" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1854,106 +1784,100 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1306</v>
+        <v>1030</v>
       </c>
       <c r="N10" t="n">
-        <v>23.53</v>
+        <v>18.56</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>3364</v>
       </c>
       <c r="P10" t="n">
-        <v>20.62</v>
+        <v>60.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>4313</v>
+        <v>2620</v>
       </c>
       <c r="R10" t="n">
-        <v>77.70999999999999</v>
+        <v>5034</v>
       </c>
       <c r="S10" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="T10" t="n">
-        <v>6975</v>
+        <v>178</v>
       </c>
       <c r="U10" t="n">
-        <v>281</v>
+        <v>15</v>
       </c>
       <c r="V10" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>542</v>
       </c>
       <c r="Z10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5652</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2620</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5034</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>176</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2</v>
       </c>
-      <c r="AA10" t="n">
-        <v>580</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8991</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>7916</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>981</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>6975</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>280</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>7</v>
-      </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>542</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>8448</v>
       </c>
       <c r="AN10" t="n">
-        <v>7</v>
+        <v>5652</v>
       </c>
       <c r="AO10" t="n">
-        <v>8991</v>
+        <v>-2900</v>
       </c>
       <c r="AP10" t="n">
-        <v>7915</v>
+        <v>-2288</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-3441</v>
+        <v>-2898</v>
       </c>
       <c r="AR10" t="n">
-        <v>-3603</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-3441</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>-3602</v>
+        <v>-2288</v>
       </c>
     </row>
     <row r="11">
@@ -1971,25 +1895,25 @@
         <v>4040</v>
       </c>
       <c r="D11" t="n">
-        <v>2717</v>
+        <v>2181</v>
       </c>
       <c r="E11" t="n">
-        <v>67.25</v>
+        <v>53.99</v>
       </c>
       <c r="F11" t="n">
-        <v>596</v>
+        <v>443</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1998,106 +1922,100 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>904</v>
+        <v>671</v>
       </c>
       <c r="N11" t="n">
-        <v>22.38</v>
+        <v>16.61</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2624</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>64.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3313</v>
+        <v>1416</v>
       </c>
       <c r="R11" t="n">
-        <v>82</v>
+        <v>3241</v>
       </c>
       <c r="S11" t="n">
-        <v>432</v>
+        <v>37</v>
       </c>
       <c r="T11" t="n">
-        <v>4389</v>
+        <v>148</v>
       </c>
       <c r="U11" t="n">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="V11" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
+        <v>453</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5361</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3797</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1418</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3241</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>148</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>6</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>468</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5634</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>5057</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>434</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>4389</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>149</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>145</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>17</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>6</v>
+        <v>453</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
-        <v>468</v>
+        <v>5361</v>
       </c>
       <c r="AN11" t="n">
-        <v>6</v>
+        <v>3795</v>
       </c>
       <c r="AO11" t="n">
-        <v>5634</v>
+        <v>-1321</v>
       </c>
       <c r="AP11" t="n">
-        <v>5055</v>
+        <v>-1173</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-1594</v>
+        <v>-1321</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1744</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-1594</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-1742</v>
+        <v>-1171</v>
       </c>
     </row>
     <row r="12">
@@ -2115,19 +2033,19 @@
         <v>2040</v>
       </c>
       <c r="D12" t="n">
-        <v>1563</v>
+        <v>1133</v>
       </c>
       <c r="E12" t="n">
-        <v>76.62</v>
+        <v>55.54</v>
       </c>
       <c r="F12" t="n">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2142,106 +2060,100 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>13.04</v>
+        <v>11.03</v>
       </c>
       <c r="O12" t="n">
+        <v>1240</v>
+      </c>
+      <c r="P12" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>751</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S12" t="n">
+        <v>13</v>
+      </c>
+      <c r="T12" t="n">
+        <v>86</v>
+      </c>
+      <c r="U12" t="n">
+        <v>70</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" t="n">
         <v>1</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1700</v>
-      </c>
-      <c r="R12" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>174</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1652</v>
-      </c>
-      <c r="U12" t="n">
-        <v>152</v>
-      </c>
-      <c r="V12" t="n">
-        <v>54</v>
-      </c>
-      <c r="W12" t="n">
-        <v>134</v>
-      </c>
-      <c r="X12" t="n">
-        <v>34</v>
-      </c>
       <c r="Y12" t="n">
+        <v>249</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2445</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1608</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>751</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1248</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>86</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
         <v>7</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AJ12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
-        <v>258</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2485</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2257</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>174</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1652</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>152</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>54</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>134</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>34</v>
-      </c>
       <c r="AK12" t="n">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="AL12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AM12" t="n">
-        <v>258</v>
+        <v>2445</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>1608</v>
       </c>
       <c r="AO12" t="n">
-        <v>2485</v>
+        <v>-405</v>
       </c>
       <c r="AP12" t="n">
-        <v>2257</v>
+        <v>-368</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-445</v>
+        <v>-405</v>
       </c>
       <c r="AR12" t="n">
-        <v>-557</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-445</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-557</v>
+        <v>-368</v>
       </c>
     </row>
     <row r="13">
@@ -2259,19 +2171,19 @@
         <v>6235</v>
       </c>
       <c r="D13" t="n">
-        <v>5075</v>
+        <v>4253</v>
       </c>
       <c r="E13" t="n">
-        <v>81.40000000000001</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1391</v>
+        <v>1149</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
@@ -2286,106 +2198,100 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>980</v>
+        <v>808</v>
       </c>
       <c r="N13" t="n">
-        <v>15.72</v>
+        <v>12.96</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5402</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>86.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>6466</v>
+        <v>1393</v>
       </c>
       <c r="R13" t="n">
-        <v>103.7</v>
+        <v>7134</v>
       </c>
       <c r="S13" t="n">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="T13" t="n">
-        <v>8976</v>
+        <v>147</v>
       </c>
       <c r="U13" t="n">
-        <v>152</v>
+        <v>10</v>
       </c>
       <c r="V13" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>44</v>
+        <v>969</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="n">
-        <v>983</v>
+        <v>9735</v>
       </c>
       <c r="AB13" t="n">
+        <v>8195</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1394</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>7134</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>54</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>146</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>969</v>
+      </c>
+      <c r="AL13" t="n">
         <v>14</v>
       </c>
-      <c r="AC13" t="n">
-        <v>10379</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>10172</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>149</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>8976</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>151</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>59</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
       <c r="AM13" t="n">
-        <v>983</v>
+        <v>9735</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>8195</v>
       </c>
       <c r="AO13" t="n">
-        <v>10379</v>
+        <v>-3500</v>
       </c>
       <c r="AP13" t="n">
-        <v>10171</v>
+        <v>-2793</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-4144</v>
+        <v>-3500</v>
       </c>
       <c r="AR13" t="n">
-        <v>-3706</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>-4144</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-3705</v>
+        <v>-2793</v>
       </c>
     </row>
     <row r="14">
@@ -2403,19 +2309,19 @@
         <v>876</v>
       </c>
       <c r="D14" t="n">
-        <v>801</v>
+        <v>723</v>
       </c>
       <c r="E14" t="n">
-        <v>91.44</v>
+        <v>82.53</v>
       </c>
       <c r="F14" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2430,28 +2336,28 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
-        <v>7.76</v>
+        <v>6.85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>812</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>92.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>908</v>
+        <v>99</v>
       </c>
       <c r="R14" t="n">
-        <v>103.65</v>
+        <v>891</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T14" t="n">
-        <v>1038</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2466,70 +2372,64 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
+        <v>1190</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1091</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>99</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>891</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>175</v>
       </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1215</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1215</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1038</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2</v>
-      </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>175</v>
+        <v>1190</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1091</v>
       </c>
       <c r="AO14" t="n">
-        <v>1215</v>
+        <v>-314</v>
       </c>
       <c r="AP14" t="n">
-        <v>1215</v>
+        <v>-279</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-339</v>
+        <v>-314</v>
       </c>
       <c r="AR14" t="n">
-        <v>-307</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>-339</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>-307</v>
+        <v>-279</v>
       </c>
     </row>
     <row r="15">
@@ -2547,133 +2447,127 @@
         <v>411</v>
       </c>
       <c r="D15" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E15" t="n">
-        <v>39.42</v>
+        <v>36.74</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>42</v>
+      </c>
+      <c r="N15" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>186</v>
+      </c>
+      <c r="P15" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>213</v>
+      </c>
+      <c r="R15" t="n">
+        <v>375</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>41</v>
-      </c>
-      <c r="N15" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="O15" t="n">
-        <v>37</v>
-      </c>
-      <c r="P15" t="n">
-        <v>78.34</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>197</v>
-      </c>
-      <c r="R15" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="S15" t="n">
-        <v>184</v>
-      </c>
-      <c r="T15" t="n">
-        <v>408</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>17</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AA15" t="n">
+        <v>626</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>404</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>213</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>375</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL15" t="n">
         <v>1</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>636</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>435</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>184</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>408</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
       <c r="AM15" t="n">
-        <v>25</v>
+        <v>626</v>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>404</v>
       </c>
       <c r="AO15" t="n">
-        <v>636</v>
+        <v>-215</v>
       </c>
       <c r="AP15" t="n">
-        <v>435</v>
+        <v>-218</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-225</v>
+        <v>-215</v>
       </c>
       <c r="AR15" t="n">
-        <v>-238</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>-225</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>-238</v>
+        <v>-218</v>
       </c>
     </row>
     <row r="16">
@@ -2691,19 +2585,19 @@
         <v>2170</v>
       </c>
       <c r="D16" t="n">
-        <v>1618</v>
+        <v>1187</v>
       </c>
       <c r="E16" t="n">
-        <v>74.56</v>
+        <v>54.7</v>
       </c>
       <c r="F16" t="n">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="G16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2718,106 +2612,100 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="N16" t="n">
-        <v>14.61</v>
+        <v>12.35</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>1410</v>
       </c>
       <c r="P16" t="n">
-        <v>3.01</v>
+        <v>64.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>1898</v>
+        <v>815</v>
       </c>
       <c r="R16" t="n">
-        <v>87.47</v>
+        <v>1522</v>
       </c>
       <c r="S16" t="n">
-        <v>275</v>
+        <v>53</v>
       </c>
       <c r="T16" t="n">
-        <v>2176</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>17</v>
+        <v>492</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>516</v>
+        <v>2921</v>
       </c>
       <c r="AB16" t="n">
+        <v>2106</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>815</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1522</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>53</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
         <v>4</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3009</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2734</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>276</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2176</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>10</v>
-      </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>492</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM16" t="n">
-        <v>516</v>
+        <v>2921</v>
       </c>
       <c r="AN16" t="n">
-        <v>4</v>
+        <v>2106</v>
       </c>
       <c r="AO16" t="n">
-        <v>3009</v>
+        <v>-751</v>
       </c>
       <c r="AP16" t="n">
-        <v>2733</v>
+        <v>-696</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-839</v>
+        <v>-751</v>
       </c>
       <c r="AR16" t="n">
-        <v>-836</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>-839</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>-835</v>
+        <v>-696</v>
       </c>
     </row>
   </sheetData>
